--- a/Data/RutaEditado_coordenadas2.xlsx
+++ b/Data/RutaEditado_coordenadas2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="657">
   <si>
     <t>tienda</t>
   </si>
@@ -1976,6 +1976,12 @@
   </si>
   <si>
     <t>PERIFERICO FRANCISCO R. ALMADA ESQ CON CALLE ZOOLOGIA NO. 1206, CHIHUAHUA, MEXICO</t>
+  </si>
+  <si>
+    <t>RELLENO SANITARIO</t>
+  </si>
+  <si>
+    <t>DIPACSA</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +2088,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -2096,6 +2102,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -3190,18 +3199,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:I224"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="21.1719" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.57812" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.67188" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.3516" style="1" customWidth="1"/>
     <col min="5" max="5" width="89" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.8516" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.3516" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.8516" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="8" max="9" width="15.8516" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13.55" customHeight="1">
@@ -3229,6 +3238,7 @@
       <c r="H1" t="s" s="2">
         <v>7</v>
       </c>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" ht="13.55" customHeight="1">
       <c r="A2" t="s" s="3">
@@ -3255,5674 +3265,5913 @@
       <c r="H2" s="4">
         <v>-106.093042334611</v>
       </c>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" t="s" s="5">
+      <c r="A3" t="s" s="6">
         <v>12</v>
       </c>
-      <c r="B3" t="s" s="5">
+      <c r="B3" t="s" s="6">
         <v>13</v>
       </c>
-      <c r="C3" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D3" s="6">
-        <v>570</v>
-      </c>
-      <c r="E3" t="s" s="5">
+      <c r="C3" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7">
+        <v>570</v>
+      </c>
+      <c r="E3" t="s" s="6">
         <v>14</v>
       </c>
-      <c r="F3" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="F3" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
         <v>28.636891526005</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="7">
         <v>-106.063222445559</v>
       </c>
+      <c r="I3" s="8"/>
     </row>
     <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" t="s" s="5">
+      <c r="A4" t="s" s="6">
         <v>15</v>
       </c>
-      <c r="B4" t="s" s="5">
+      <c r="B4" t="s" s="6">
         <v>16</v>
       </c>
-      <c r="C4" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6">
-        <v>570</v>
-      </c>
-      <c r="E4" t="s" s="5">
+      <c r="C4" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7">
+        <v>570</v>
+      </c>
+      <c r="E4" t="s" s="6">
         <v>17</v>
       </c>
-      <c r="F4" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="F4" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
         <v>28.7253025598789</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="7">
         <v>-106.122607641142</v>
       </c>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" t="s" s="5">
+      <c r="A5" t="s" s="6">
         <v>18</v>
       </c>
-      <c r="B5" t="s" s="5">
+      <c r="B5" t="s" s="6">
         <v>19</v>
       </c>
-      <c r="C5" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D5" s="6">
-        <v>570</v>
-      </c>
-      <c r="E5" t="s" s="5">
+      <c r="C5" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7">
+        <v>570</v>
+      </c>
+      <c r="E5" t="s" s="6">
         <v>20</v>
       </c>
-      <c r="F5" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="F5" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
         <v>28.6892212559343</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>-106.084301572832</v>
       </c>
+      <c r="I5" s="8"/>
     </row>
     <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" t="s" s="5">
+      <c r="A6" t="s" s="6">
         <v>21</v>
       </c>
-      <c r="B6" t="s" s="5">
+      <c r="B6" t="s" s="6">
         <v>22</v>
       </c>
-      <c r="C6" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D6" s="6">
-        <v>570</v>
-      </c>
-      <c r="E6" t="s" s="5">
+      <c r="C6" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7">
+        <v>570</v>
+      </c>
+      <c r="E6" t="s" s="6">
         <v>23</v>
       </c>
-      <c r="F6" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
         <v>28.6491768721202</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <v>-106.011321321927</v>
       </c>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" t="s" s="5">
+      <c r="A7" t="s" s="6">
         <v>24</v>
       </c>
-      <c r="B7" t="s" s="5">
+      <c r="B7" t="s" s="6">
         <v>25</v>
       </c>
-      <c r="C7" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D7" s="6">
-        <v>570</v>
-      </c>
-      <c r="E7" t="s" s="5">
+      <c r="C7" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7">
+        <v>570</v>
+      </c>
+      <c r="E7" t="s" s="6">
         <v>26</v>
       </c>
-      <c r="F7" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="F7" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
         <v>28.7252345872144</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <v>-106.122582778901</v>
       </c>
+      <c r="I7" s="8"/>
     </row>
     <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" t="s" s="5">
+      <c r="A8" t="s" s="6">
         <v>27</v>
       </c>
-      <c r="B8" t="s" s="5">
+      <c r="B8" t="s" s="6">
         <v>28</v>
       </c>
-      <c r="C8" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D8" s="6">
-        <v>570</v>
-      </c>
-      <c r="E8" t="s" s="5">
+      <c r="C8" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7">
+        <v>570</v>
+      </c>
+      <c r="E8" t="s" s="6">
         <v>29</v>
       </c>
-      <c r="F8" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="F8" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
         <v>28.6341236667054</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>-106.077842072674</v>
       </c>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" t="s" s="5">
+      <c r="A9" t="s" s="6">
         <v>30</v>
       </c>
-      <c r="B9" t="s" s="5">
+      <c r="B9" t="s" s="6">
         <v>31</v>
       </c>
-      <c r="C9" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D9" s="6">
-        <v>570</v>
-      </c>
-      <c r="E9" t="s" s="5">
+      <c r="C9" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D9" s="7">
+        <v>570</v>
+      </c>
+      <c r="E9" t="s" s="6">
         <v>32</v>
       </c>
-      <c r="F9" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="F9" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7">
         <v>28.6059598832859</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <v>-106.102741284432</v>
       </c>
+      <c r="I9" s="8"/>
     </row>
     <row r="10" ht="13.55" customHeight="1">
-      <c r="A10" t="s" s="5">
+      <c r="A10" t="s" s="6">
         <v>33</v>
       </c>
-      <c r="B10" t="s" s="5">
+      <c r="B10" t="s" s="6">
         <v>34</v>
       </c>
-      <c r="C10" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6">
-        <v>570</v>
-      </c>
-      <c r="E10" t="s" s="5">
+      <c r="C10" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D10" s="7">
+        <v>570</v>
+      </c>
+      <c r="E10" t="s" s="6">
         <v>35</v>
       </c>
-      <c r="F10" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="F10" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7">
         <v>28.6326230159152</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <v>-106.076214999272</v>
       </c>
+      <c r="I10" s="8"/>
     </row>
     <row r="11" ht="13.55" customHeight="1">
-      <c r="A11" t="s" s="5">
+      <c r="A11" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="B11" t="s" s="5">
+      <c r="B11" t="s" s="6">
         <v>37</v>
       </c>
-      <c r="C11" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D11" s="6">
-        <v>570</v>
-      </c>
-      <c r="E11" t="s" s="5">
+      <c r="C11" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D11" s="7">
+        <v>570</v>
+      </c>
+      <c r="E11" t="s" s="6">
         <v>38</v>
       </c>
-      <c r="F11" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
+      <c r="F11" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7">
         <v>28.6752057699494</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="7">
         <v>-106.135178513074</v>
       </c>
+      <c r="I11" s="8"/>
     </row>
     <row r="12" ht="13.55" customHeight="1">
-      <c r="A12" t="s" s="5">
+      <c r="A12" t="s" s="6">
         <v>39</v>
       </c>
-      <c r="B12" t="s" s="5">
+      <c r="B12" t="s" s="6">
         <v>40</v>
       </c>
-      <c r="C12" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D12" s="6">
-        <v>570</v>
-      </c>
-      <c r="E12" t="s" s="5">
+      <c r="C12" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D12" s="7">
+        <v>570</v>
+      </c>
+      <c r="E12" t="s" s="6">
         <v>41</v>
       </c>
-      <c r="F12" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="F12" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7">
         <v>28.7772356716519</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="7">
         <v>-106.167453803602</v>
       </c>
+      <c r="I12" s="8"/>
     </row>
     <row r="13" ht="13.55" customHeight="1">
-      <c r="A13" t="s" s="5">
+      <c r="A13" t="s" s="6">
         <v>42</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D13" s="6">
-        <v>570</v>
-      </c>
-      <c r="E13" t="s" s="5">
+      <c r="B13" s="8"/>
+      <c r="C13" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D13" s="7">
+        <v>570</v>
+      </c>
+      <c r="E13" t="s" s="6">
         <v>43</v>
       </c>
-      <c r="F13" t="b" s="6">
+      <c r="F13" t="b" s="7">
         <v>1</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="7">
         <v>28.6428989843273</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="7">
         <v>-106.085440466649</v>
       </c>
+      <c r="I13" s="8"/>
     </row>
     <row r="14" ht="13.55" customHeight="1">
-      <c r="A14" t="s" s="5">
+      <c r="A14" t="s" s="6">
         <v>44</v>
       </c>
-      <c r="B14" t="s" s="5">
+      <c r="B14" t="s" s="6">
         <v>45</v>
       </c>
-      <c r="C14" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D14" s="6">
-        <v>570</v>
-      </c>
-      <c r="E14" t="s" s="5">
+      <c r="C14" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D14" s="7">
+        <v>570</v>
+      </c>
+      <c r="E14" t="s" s="6">
         <v>46</v>
       </c>
-      <c r="F14" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="F14" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7">
         <v>28.6533925491599</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="7">
         <v>-106.115665942787</v>
       </c>
+      <c r="I14" s="8"/>
     </row>
     <row r="15" ht="13.55" customHeight="1">
-      <c r="A15" t="s" s="5">
+      <c r="A15" t="s" s="6">
         <v>47</v>
       </c>
-      <c r="B15" t="s" s="5">
+      <c r="B15" t="s" s="6">
         <v>48</v>
       </c>
-      <c r="C15" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D15" s="6">
-        <v>570</v>
-      </c>
-      <c r="E15" t="s" s="5">
+      <c r="C15" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D15" s="7">
+        <v>570</v>
+      </c>
+      <c r="E15" t="s" s="6">
         <v>49</v>
       </c>
-      <c r="F15" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="F15" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
         <v>28.5862381767676</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="7">
         <v>-105.960645964289</v>
       </c>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" ht="13.55" customHeight="1">
-      <c r="A16" t="s" s="5">
+      <c r="A16" t="s" s="6">
         <v>50</v>
       </c>
-      <c r="B16" t="s" s="5">
+      <c r="B16" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="C16" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D16" s="6">
-        <v>570</v>
-      </c>
-      <c r="E16" t="s" s="5">
+      <c r="C16" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D16" s="7">
+        <v>570</v>
+      </c>
+      <c r="E16" t="s" s="6">
         <v>52</v>
       </c>
-      <c r="F16" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="F16" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7">
         <v>28.6616048343202</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="7">
         <v>-106.117875335510</v>
       </c>
+      <c r="I16" s="8"/>
     </row>
     <row r="17" ht="13.55" customHeight="1">
-      <c r="A17" t="s" s="5">
+      <c r="A17" t="s" s="6">
         <v>53</v>
       </c>
-      <c r="B17" t="s" s="5">
+      <c r="B17" t="s" s="6">
         <v>54</v>
       </c>
-      <c r="C17" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D17" s="6">
-        <v>570</v>
-      </c>
-      <c r="E17" t="s" s="5">
+      <c r="C17" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D17" s="7">
+        <v>570</v>
+      </c>
+      <c r="E17" t="s" s="6">
         <v>55</v>
       </c>
-      <c r="F17" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6">
+      <c r="F17" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7">
         <v>28.7337708286859</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="7">
         <v>-106.100251985187</v>
       </c>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" ht="13.55" customHeight="1">
-      <c r="A18" t="s" s="5">
+      <c r="A18" t="s" s="6">
         <v>56</v>
       </c>
-      <c r="B18" t="s" s="5">
+      <c r="B18" t="s" s="6">
         <v>57</v>
       </c>
-      <c r="C18" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D18" s="6">
-        <v>570</v>
-      </c>
-      <c r="E18" t="s" s="5">
+      <c r="C18" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D18" s="7">
+        <v>570</v>
+      </c>
+      <c r="E18" t="s" s="6">
         <v>58</v>
       </c>
-      <c r="F18" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="F18" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7">
         <v>28.6293028851528</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="7">
         <v>-106.082609176464</v>
       </c>
+      <c r="I18" s="8"/>
     </row>
     <row r="19" ht="13.55" customHeight="1">
-      <c r="A19" t="s" s="5">
+      <c r="A19" t="s" s="6">
         <v>59</v>
       </c>
-      <c r="B19" t="s" s="5">
+      <c r="B19" t="s" s="6">
         <v>60</v>
       </c>
-      <c r="C19" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D19" s="6">
-        <v>570</v>
-      </c>
-      <c r="E19" t="s" s="5">
+      <c r="C19" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D19" s="7">
+        <v>570</v>
+      </c>
+      <c r="E19" t="s" s="6">
         <v>61</v>
       </c>
-      <c r="F19" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6">
+      <c r="F19" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7">
         <v>28.6147146313194</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="7">
         <v>-106.1057809451</v>
       </c>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" ht="13.55" customHeight="1">
-      <c r="A20" t="s" s="5">
+      <c r="A20" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="B20" t="s" s="5">
+      <c r="B20" t="s" s="6">
         <v>63</v>
       </c>
-      <c r="C20" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D20" s="6">
-        <v>570</v>
-      </c>
-      <c r="E20" t="s" s="5">
+      <c r="C20" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D20" s="7">
+        <v>570</v>
+      </c>
+      <c r="E20" t="s" s="6">
         <v>64</v>
       </c>
-      <c r="F20" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="F20" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7">
         <v>28.5721566127499</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="7">
         <v>-106.137233621328</v>
       </c>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" ht="13.55" customHeight="1">
-      <c r="A21" t="s" s="5">
+      <c r="A21" t="s" s="6">
         <v>65</v>
       </c>
-      <c r="B21" t="s" s="5">
+      <c r="B21" t="s" s="6">
         <v>66</v>
       </c>
-      <c r="C21" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D21" s="6">
-        <v>570</v>
-      </c>
-      <c r="E21" t="s" s="5">
+      <c r="C21" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D21" s="7">
+        <v>570</v>
+      </c>
+      <c r="E21" t="s" s="6">
         <v>67</v>
       </c>
-      <c r="F21" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="F21" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7">
         <v>28.6966356489583</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="7">
         <v>-106.119179760247</v>
       </c>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" ht="13.55" customHeight="1">
-      <c r="A22" t="s" s="5">
+      <c r="A22" t="s" s="6">
         <v>68</v>
       </c>
-      <c r="B22" t="s" s="5">
+      <c r="B22" t="s" s="6">
         <v>69</v>
       </c>
-      <c r="C22" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D22" s="6">
-        <v>570</v>
-      </c>
-      <c r="E22" t="s" s="5">
+      <c r="C22" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D22" s="7">
+        <v>570</v>
+      </c>
+      <c r="E22" t="s" s="6">
         <v>70</v>
       </c>
-      <c r="F22" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="F22" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7">
         <v>28.6704359433121</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="7">
         <v>-106.132959208866</v>
       </c>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" ht="13.55" customHeight="1">
-      <c r="A23" t="s" s="5">
+      <c r="A23" t="s" s="6">
         <v>71</v>
       </c>
-      <c r="B23" t="s" s="5">
+      <c r="B23" t="s" s="6">
         <v>72</v>
       </c>
-      <c r="C23" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D23" s="6">
-        <v>570</v>
-      </c>
-      <c r="E23" t="s" s="5">
+      <c r="C23" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D23" s="7">
+        <v>570</v>
+      </c>
+      <c r="E23" t="s" s="6">
         <v>73</v>
       </c>
-      <c r="F23" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6">
+      <c r="F23" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7">
         <v>28.6650856483253</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="7">
         <v>-106.131531343682</v>
       </c>
+      <c r="I23" s="8"/>
     </row>
     <row r="24" ht="13.55" customHeight="1">
-      <c r="A24" t="s" s="5">
+      <c r="A24" t="s" s="6">
         <v>74</v>
       </c>
-      <c r="B24" t="s" s="5">
+      <c r="B24" t="s" s="6">
         <v>75</v>
       </c>
-      <c r="C24" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D24" s="6">
-        <v>570</v>
-      </c>
-      <c r="E24" t="s" s="5">
+      <c r="C24" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D24" s="7">
+        <v>570</v>
+      </c>
+      <c r="E24" t="s" s="6">
         <v>76</v>
       </c>
-      <c r="F24" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="F24" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
         <v>28.6563042933274</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="7">
         <v>-106.107600664261</v>
       </c>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" ht="13.55" customHeight="1">
-      <c r="A25" t="s" s="5">
+      <c r="A25" t="s" s="6">
         <v>77</v>
       </c>
-      <c r="B25" t="s" s="5">
+      <c r="B25" t="s" s="6">
         <v>78</v>
       </c>
-      <c r="C25" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D25" s="6">
-        <v>570</v>
-      </c>
-      <c r="E25" t="s" s="5">
+      <c r="C25" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D25" s="7">
+        <v>570</v>
+      </c>
+      <c r="E25" t="s" s="6">
         <v>79</v>
       </c>
-      <c r="F25" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6">
+      <c r="F25" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7">
         <v>28.7218993136183</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="7">
         <v>-106.148188472465</v>
       </c>
+      <c r="I25" s="8"/>
     </row>
     <row r="26" ht="13.55" customHeight="1">
-      <c r="A26" t="s" s="5">
+      <c r="A26" t="s" s="6">
         <v>80</v>
       </c>
-      <c r="B26" t="s" s="5">
+      <c r="B26" t="s" s="6">
         <v>81</v>
       </c>
-      <c r="C26" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D26" s="6">
-        <v>570</v>
-      </c>
-      <c r="E26" t="s" s="5">
+      <c r="C26" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D26" s="7">
+        <v>570</v>
+      </c>
+      <c r="E26" t="s" s="6">
         <v>82</v>
       </c>
-      <c r="F26" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="6">
+      <c r="F26" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7">
         <v>28.6678375725137</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="7">
         <v>-105.988866193693</v>
       </c>
+      <c r="I26" s="8"/>
     </row>
     <row r="27" ht="13.55" customHeight="1">
-      <c r="A27" t="s" s="5">
+      <c r="A27" t="s" s="6">
         <v>83</v>
       </c>
-      <c r="B27" t="s" s="5">
+      <c r="B27" t="s" s="6">
         <v>84</v>
       </c>
-      <c r="C27" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D27" s="6">
-        <v>570</v>
-      </c>
-      <c r="E27" t="s" s="5">
+      <c r="C27" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D27" s="7">
+        <v>570</v>
+      </c>
+      <c r="E27" t="s" s="6">
         <v>85</v>
       </c>
-      <c r="F27" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6">
+      <c r="F27" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7">
         <v>28.6440649389086</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="7">
         <v>-106.110152695785</v>
       </c>
+      <c r="I27" s="8"/>
     </row>
     <row r="28" ht="13.55" customHeight="1">
-      <c r="A28" t="s" s="5">
+      <c r="A28" t="s" s="6">
         <v>86</v>
       </c>
-      <c r="B28" t="s" s="5">
+      <c r="B28" t="s" s="6">
         <v>87</v>
       </c>
-      <c r="C28" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D28" s="6">
-        <v>570</v>
-      </c>
-      <c r="E28" t="s" s="5">
+      <c r="C28" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D28" s="7">
+        <v>570</v>
+      </c>
+      <c r="E28" t="s" s="6">
         <v>88</v>
       </c>
-      <c r="F28" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6">
+      <c r="F28" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7">
         <v>28.615092412780</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="7">
         <v>-106.097935182724</v>
       </c>
+      <c r="I28" s="8"/>
     </row>
     <row r="29" ht="13.55" customHeight="1">
-      <c r="A29" t="s" s="5">
+      <c r="A29" t="s" s="6">
         <v>89</v>
       </c>
-      <c r="B29" t="s" s="5">
+      <c r="B29" t="s" s="6">
         <v>90</v>
       </c>
-      <c r="C29" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D29" s="6">
-        <v>570</v>
-      </c>
-      <c r="E29" t="s" s="5">
+      <c r="C29" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D29" s="7">
+        <v>570</v>
+      </c>
+      <c r="E29" t="s" s="6">
         <v>91</v>
       </c>
-      <c r="F29" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G29" s="6">
+      <c r="F29" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7">
         <v>28.6351678618386</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="7">
         <v>-106.1050063102</v>
       </c>
+      <c r="I29" s="8"/>
     </row>
     <row r="30" ht="13.55" customHeight="1">
-      <c r="A30" t="s" s="5">
+      <c r="A30" t="s" s="6">
         <v>92</v>
       </c>
-      <c r="B30" t="s" s="5">
+      <c r="B30" t="s" s="6">
         <v>93</v>
       </c>
-      <c r="C30" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D30" s="6">
-        <v>570</v>
-      </c>
-      <c r="E30" t="s" s="5">
+      <c r="C30" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D30" s="7">
+        <v>570</v>
+      </c>
+      <c r="E30" t="s" s="6">
         <v>94</v>
       </c>
-      <c r="F30" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G30" s="6">
+      <c r="F30" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
         <v>28.7000440303492</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="7">
         <v>-106.142649244994</v>
       </c>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" ht="13.55" customHeight="1">
-      <c r="A31" t="s" s="5">
+      <c r="A31" t="s" s="6">
         <v>95</v>
       </c>
-      <c r="B31" t="s" s="5">
+      <c r="B31" t="s" s="6">
         <v>96</v>
       </c>
-      <c r="C31" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D31" s="6">
-        <v>570</v>
-      </c>
-      <c r="E31" t="s" s="5">
+      <c r="C31" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D31" s="7">
+        <v>570</v>
+      </c>
+      <c r="E31" t="s" s="6">
         <v>97</v>
       </c>
-      <c r="F31" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G31" s="6">
+      <c r="F31" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7">
         <v>28.7021809129663</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="7">
         <v>-106.142312905266</v>
       </c>
+      <c r="I31" s="8"/>
     </row>
     <row r="32" ht="13.55" customHeight="1">
-      <c r="A32" t="s" s="5">
+      <c r="A32" t="s" s="6">
         <v>98</v>
       </c>
-      <c r="B32" t="s" s="5">
+      <c r="B32" t="s" s="6">
         <v>99</v>
       </c>
-      <c r="C32" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D32" s="6">
-        <v>570</v>
-      </c>
-      <c r="E32" t="s" s="5">
+      <c r="C32" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D32" s="7">
+        <v>570</v>
+      </c>
+      <c r="E32" t="s" s="6">
         <v>100</v>
       </c>
-      <c r="F32" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G32" s="6">
+      <c r="F32" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7">
         <v>28.6518927032388</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="7">
         <v>-106.103966099336</v>
       </c>
+      <c r="I32" s="8"/>
     </row>
     <row r="33" ht="13.55" customHeight="1">
-      <c r="A33" t="s" s="5">
+      <c r="A33" t="s" s="6">
         <v>101</v>
       </c>
-      <c r="B33" t="s" s="5">
+      <c r="B33" t="s" s="6">
         <v>102</v>
       </c>
-      <c r="C33" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D33" s="6">
-        <v>570</v>
-      </c>
-      <c r="E33" t="s" s="5">
+      <c r="C33" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D33" s="7">
+        <v>570</v>
+      </c>
+      <c r="E33" t="s" s="6">
         <v>103</v>
       </c>
-      <c r="F33" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G33" s="6">
+      <c r="F33" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7">
         <v>28.7130393799473</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="7">
         <v>-106.091944664819</v>
       </c>
+      <c r="I33" s="8"/>
     </row>
     <row r="34" ht="13.55" customHeight="1">
-      <c r="A34" t="s" s="5">
+      <c r="A34" t="s" s="6">
         <v>104</v>
       </c>
-      <c r="B34" t="s" s="5">
+      <c r="B34" t="s" s="6">
         <v>105</v>
       </c>
-      <c r="C34" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D34" s="6">
-        <v>570</v>
-      </c>
-      <c r="E34" t="s" s="5">
+      <c r="C34" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D34" s="7">
+        <v>570</v>
+      </c>
+      <c r="E34" t="s" s="6">
         <v>106</v>
       </c>
-      <c r="F34" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G34" s="6">
+      <c r="F34" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7">
         <v>28.611087491902</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="7">
         <v>-106.082639836508</v>
       </c>
+      <c r="I34" s="8"/>
     </row>
     <row r="35" ht="13.55" customHeight="1">
-      <c r="A35" t="s" s="5">
+      <c r="A35" t="s" s="6">
         <v>107</v>
       </c>
-      <c r="B35" t="s" s="5">
+      <c r="B35" t="s" s="6">
         <v>108</v>
       </c>
-      <c r="C35" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D35" s="6">
-        <v>570</v>
-      </c>
-      <c r="E35" t="s" s="5">
+      <c r="C35" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D35" s="7">
+        <v>570</v>
+      </c>
+      <c r="E35" t="s" s="6">
         <v>109</v>
       </c>
-      <c r="F35" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="F35" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7">
         <v>28.6687615186061</v>
       </c>
-      <c r="H35" s="6">
+      <c r="H35" s="7">
         <v>-106.117135836863</v>
       </c>
+      <c r="I35" s="8"/>
     </row>
     <row r="36" ht="13.55" customHeight="1">
-      <c r="A36" t="s" s="5">
+      <c r="A36" t="s" s="6">
         <v>110</v>
       </c>
-      <c r="B36" t="s" s="5">
+      <c r="B36" t="s" s="6">
         <v>111</v>
       </c>
-      <c r="C36" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D36" s="6">
-        <v>570</v>
-      </c>
-      <c r="E36" t="s" s="5">
+      <c r="C36" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D36" s="7">
+        <v>570</v>
+      </c>
+      <c r="E36" t="s" s="6">
         <v>112</v>
       </c>
-      <c r="F36" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G36" s="6">
+      <c r="F36" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G36" s="7">
         <v>28.6458574072933</v>
       </c>
-      <c r="H36" s="6">
+      <c r="H36" s="7">
         <v>-106.117121561465</v>
       </c>
+      <c r="I36" s="8"/>
     </row>
     <row r="37" ht="13.55" customHeight="1">
-      <c r="A37" t="s" s="5">
+      <c r="A37" t="s" s="6">
         <v>113</v>
       </c>
-      <c r="B37" t="s" s="5">
+      <c r="B37" t="s" s="6">
         <v>114</v>
       </c>
-      <c r="C37" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D37" s="6">
-        <v>570</v>
-      </c>
-      <c r="E37" t="s" s="5">
+      <c r="C37" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D37" s="7">
+        <v>570</v>
+      </c>
+      <c r="E37" t="s" s="6">
         <v>115</v>
       </c>
-      <c r="F37" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G37" s="6">
+      <c r="F37" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G37" s="7">
         <v>28.6707924573666</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37" s="7">
         <v>-106.095496485655</v>
       </c>
+      <c r="I37" s="8"/>
     </row>
     <row r="38" ht="13.55" customHeight="1">
-      <c r="A38" t="s" s="5">
+      <c r="A38" t="s" s="6">
         <v>116</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="6">
-        <v>570</v>
-      </c>
-      <c r="E38" t="s" s="5">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="7">
+        <v>570</v>
+      </c>
+      <c r="E38" t="s" s="6">
         <v>117</v>
       </c>
-      <c r="F38" t="b" s="6">
+      <c r="F38" t="b" s="7">
         <v>1</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="7">
         <v>28.6497806856128</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="7">
         <v>-106.028521839699</v>
       </c>
+      <c r="I38" s="8"/>
     </row>
     <row r="39" ht="13.55" customHeight="1">
-      <c r="A39" t="s" s="5">
+      <c r="A39" t="s" s="6">
         <v>118</v>
       </c>
-      <c r="B39" t="s" s="5">
+      <c r="B39" t="s" s="6">
         <v>119</v>
       </c>
-      <c r="C39" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D39" s="6">
-        <v>570</v>
-      </c>
-      <c r="E39" t="s" s="5">
+      <c r="C39" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D39" s="7">
+        <v>570</v>
+      </c>
+      <c r="E39" t="s" s="6">
         <v>120</v>
       </c>
-      <c r="F39" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G39" s="6">
+      <c r="F39" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7">
         <v>28.7814072153871</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="7">
         <v>-106.168986054371</v>
       </c>
+      <c r="I39" s="8"/>
     </row>
     <row r="40" ht="13.55" customHeight="1">
-      <c r="A40" t="s" s="5">
+      <c r="A40" t="s" s="6">
         <v>121</v>
       </c>
-      <c r="B40" t="s" s="5">
+      <c r="B40" t="s" s="6">
         <v>122</v>
       </c>
-      <c r="C40" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D40" s="6">
-        <v>570</v>
-      </c>
-      <c r="E40" t="s" s="5">
+      <c r="C40" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D40" s="7">
+        <v>570</v>
+      </c>
+      <c r="E40" t="s" s="6">
         <v>123</v>
       </c>
-      <c r="F40" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G40" s="6">
+      <c r="F40" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7">
         <v>28.6892759773573</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="7">
         <v>-106.132136295922</v>
       </c>
+      <c r="I40" s="8"/>
     </row>
     <row r="41" ht="13.55" customHeight="1">
-      <c r="A41" t="s" s="5">
+      <c r="A41" t="s" s="6">
         <v>124</v>
       </c>
-      <c r="B41" t="s" s="5">
+      <c r="B41" t="s" s="6">
         <v>125</v>
       </c>
-      <c r="C41" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D41" s="6">
-        <v>570</v>
-      </c>
-      <c r="E41" t="s" s="5">
+      <c r="C41" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D41" s="7">
+        <v>570</v>
+      </c>
+      <c r="E41" t="s" s="6">
         <v>126</v>
       </c>
-      <c r="F41" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G41" s="6">
+      <c r="F41" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7">
         <v>28.7020800589015</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="7">
         <v>-106.149159666553</v>
       </c>
+      <c r="I41" s="8"/>
     </row>
     <row r="42" ht="13.55" customHeight="1">
-      <c r="A42" t="s" s="5">
+      <c r="A42" t="s" s="6">
         <v>127</v>
       </c>
-      <c r="B42" t="s" s="5">
+      <c r="B42" t="s" s="6">
         <v>128</v>
       </c>
-      <c r="C42" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D42" s="6">
-        <v>570</v>
-      </c>
-      <c r="E42" t="s" s="5">
+      <c r="C42" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D42" s="7">
+        <v>570</v>
+      </c>
+      <c r="E42" t="s" s="6">
         <v>129</v>
       </c>
-      <c r="F42" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G42" s="6">
+      <c r="F42" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7">
         <v>28.704932703242</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="7">
         <v>-106.149270373341</v>
       </c>
+      <c r="I42" s="8"/>
     </row>
     <row r="43" ht="13.55" customHeight="1">
-      <c r="A43" t="s" s="5">
+      <c r="A43" t="s" s="6">
         <v>130</v>
       </c>
-      <c r="B43" t="s" s="5">
+      <c r="B43" t="s" s="6">
         <v>131</v>
       </c>
-      <c r="C43" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D43" s="6">
-        <v>570</v>
-      </c>
-      <c r="E43" t="s" s="5">
+      <c r="C43" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D43" s="7">
+        <v>570</v>
+      </c>
+      <c r="E43" t="s" s="6">
         <v>132</v>
       </c>
-      <c r="F43" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G43" s="6">
+      <c r="F43" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7">
         <v>28.6736574770878</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="7">
         <v>-106.090988977807</v>
       </c>
+      <c r="I43" s="8"/>
     </row>
     <row r="44" ht="13.55" customHeight="1">
-      <c r="A44" t="s" s="5">
+      <c r="A44" t="s" s="6">
         <v>133</v>
       </c>
-      <c r="B44" t="s" s="5">
+      <c r="B44" t="s" s="6">
         <v>134</v>
       </c>
-      <c r="C44" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D44" s="6">
-        <v>570</v>
-      </c>
-      <c r="E44" t="s" s="5">
+      <c r="C44" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D44" s="7">
+        <v>570</v>
+      </c>
+      <c r="E44" t="s" s="6">
         <v>135</v>
       </c>
-      <c r="F44" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G44" s="6">
+      <c r="F44" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7">
         <v>28.6051538211217</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="7">
         <v>-106.095434554815</v>
       </c>
+      <c r="I44" s="8"/>
     </row>
     <row r="45" ht="13.55" customHeight="1">
-      <c r="A45" t="s" s="5">
+      <c r="A45" t="s" s="6">
         <v>136</v>
       </c>
-      <c r="B45" t="s" s="5">
+      <c r="B45" t="s" s="6">
         <v>137</v>
       </c>
-      <c r="C45" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D45" s="6">
-        <v>570</v>
-      </c>
-      <c r="E45" t="s" s="5">
+      <c r="C45" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D45" s="7">
+        <v>570</v>
+      </c>
+      <c r="E45" t="s" s="6">
         <v>138</v>
       </c>
-      <c r="F45" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G45" s="6">
+      <c r="F45" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7">
         <v>28.6301394493967</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="7">
         <v>-106.075497657515</v>
       </c>
+      <c r="I45" s="8"/>
     </row>
     <row r="46" ht="13.55" customHeight="1">
-      <c r="A46" t="s" s="5">
+      <c r="A46" t="s" s="6">
         <v>139</v>
       </c>
-      <c r="B46" t="s" s="5">
+      <c r="B46" t="s" s="6">
         <v>140</v>
       </c>
-      <c r="C46" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D46" s="6">
-        <v>570</v>
-      </c>
-      <c r="E46" t="s" s="5">
+      <c r="C46" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D46" s="7">
+        <v>570</v>
+      </c>
+      <c r="E46" t="s" s="6">
         <v>141</v>
       </c>
-      <c r="F46" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G46" s="6">
+      <c r="F46" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G46" s="7">
         <v>28.6419532527554</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="7">
         <v>-106.068084308293</v>
       </c>
+      <c r="I46" s="8"/>
     </row>
     <row r="47" ht="13.55" customHeight="1">
-      <c r="A47" t="s" s="5">
+      <c r="A47" t="s" s="6">
         <v>142</v>
       </c>
-      <c r="B47" t="s" s="5">
+      <c r="B47" t="s" s="6">
         <v>143</v>
       </c>
-      <c r="C47" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D47" s="6">
-        <v>570</v>
-      </c>
-      <c r="E47" t="s" s="5">
+      <c r="C47" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D47" s="7">
+        <v>570</v>
+      </c>
+      <c r="E47" t="s" s="6">
         <v>144</v>
       </c>
-      <c r="F47" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G47" s="6">
+      <c r="F47" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7">
         <v>28.6920823373585</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="7">
         <v>-106.114891254239</v>
       </c>
+      <c r="I47" s="8"/>
     </row>
     <row r="48" ht="13.55" customHeight="1">
-      <c r="A48" t="s" s="5">
+      <c r="A48" t="s" s="6">
         <v>145</v>
       </c>
-      <c r="B48" t="s" s="5">
+      <c r="B48" t="s" s="6">
         <v>146</v>
       </c>
-      <c r="C48" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D48" s="6">
-        <v>570</v>
-      </c>
-      <c r="E48" t="s" s="5">
+      <c r="C48" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D48" s="7">
+        <v>570</v>
+      </c>
+      <c r="E48" t="s" s="6">
         <v>147</v>
       </c>
-      <c r="F48" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G48" s="6">
+      <c r="F48" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7">
         <v>28.6559832067299</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="7">
         <v>-106.078472398834</v>
       </c>
+      <c r="I48" s="8"/>
     </row>
     <row r="49" ht="13.55" customHeight="1">
-      <c r="A49" t="s" s="5">
+      <c r="A49" t="s" s="6">
         <v>148</v>
       </c>
-      <c r="B49" t="s" s="5">
+      <c r="B49" t="s" s="6">
         <v>149</v>
       </c>
-      <c r="C49" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D49" s="6">
-        <v>570</v>
-      </c>
-      <c r="E49" t="s" s="5">
+      <c r="C49" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D49" s="7">
+        <v>570</v>
+      </c>
+      <c r="E49" t="s" s="6">
         <v>150</v>
       </c>
-      <c r="F49" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G49" s="6">
+      <c r="F49" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7">
         <v>28.6444266153071</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H49" s="7">
         <v>-106.099768659024</v>
       </c>
+      <c r="I49" s="8"/>
     </row>
     <row r="50" ht="13.55" customHeight="1">
-      <c r="A50" t="s" s="5">
+      <c r="A50" t="s" s="6">
         <v>151</v>
       </c>
-      <c r="B50" t="s" s="5">
+      <c r="B50" t="s" s="6">
         <v>152</v>
       </c>
-      <c r="C50" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D50" s="6">
-        <v>570</v>
-      </c>
-      <c r="E50" t="s" s="5">
+      <c r="C50" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D50" s="7">
+        <v>570</v>
+      </c>
+      <c r="E50" t="s" s="6">
         <v>153</v>
       </c>
-      <c r="F50" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G50" s="6">
+      <c r="F50" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7">
         <v>28.6450265273693</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H50" s="7">
         <v>-106.091939787388</v>
       </c>
+      <c r="I50" s="8"/>
     </row>
     <row r="51" ht="13.55" customHeight="1">
-      <c r="A51" t="s" s="5">
+      <c r="A51" t="s" s="6">
         <v>154</v>
       </c>
-      <c r="B51" t="s" s="5">
+      <c r="B51" t="s" s="6">
         <v>155</v>
       </c>
-      <c r="C51" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D51" s="6">
-        <v>570</v>
-      </c>
-      <c r="E51" t="s" s="5">
+      <c r="C51" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D51" s="7">
+        <v>570</v>
+      </c>
+      <c r="E51" t="s" s="6">
         <v>156</v>
       </c>
-      <c r="F51" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G51" s="6">
+      <c r="F51" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7">
         <v>28.6475622806198</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="7">
         <v>-106.112832967597</v>
       </c>
+      <c r="I51" s="8"/>
     </row>
     <row r="52" ht="13.55" customHeight="1">
-      <c r="A52" t="s" s="5">
+      <c r="A52" t="s" s="6">
         <v>157</v>
       </c>
-      <c r="B52" t="s" s="5">
+      <c r="B52" t="s" s="6">
         <v>158</v>
       </c>
-      <c r="C52" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D52" s="6">
-        <v>570</v>
-      </c>
-      <c r="E52" t="s" s="5">
+      <c r="C52" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D52" s="7">
+        <v>570</v>
+      </c>
+      <c r="E52" t="s" s="6">
         <v>159</v>
       </c>
-      <c r="F52" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G52" s="6">
+      <c r="F52" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7">
         <v>28.6771039102678</v>
       </c>
-      <c r="H52" s="6">
+      <c r="H52" s="7">
         <v>-106.079828918503</v>
       </c>
+      <c r="I52" s="8"/>
     </row>
     <row r="53" ht="13.55" customHeight="1">
-      <c r="A53" t="s" s="5">
+      <c r="A53" t="s" s="6">
         <v>160</v>
       </c>
-      <c r="B53" t="s" s="5">
+      <c r="B53" t="s" s="6">
         <v>161</v>
       </c>
-      <c r="C53" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D53" s="6">
-        <v>570</v>
-      </c>
-      <c r="E53" t="s" s="5">
+      <c r="C53" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D53" s="7">
+        <v>570</v>
+      </c>
+      <c r="E53" t="s" s="6">
         <v>162</v>
       </c>
-      <c r="F53" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G53" s="6">
+      <c r="F53" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G53" s="7">
         <v>28.7269807384385</v>
       </c>
-      <c r="H53" s="6">
+      <c r="H53" s="7">
         <v>-106.117869321210</v>
       </c>
+      <c r="I53" s="8"/>
     </row>
     <row r="54" ht="13.55" customHeight="1">
-      <c r="A54" t="s" s="5">
+      <c r="A54" t="s" s="6">
         <v>163</v>
       </c>
-      <c r="B54" t="s" s="5">
+      <c r="B54" t="s" s="6">
         <v>164</v>
       </c>
-      <c r="C54" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D54" s="6">
-        <v>570</v>
-      </c>
-      <c r="E54" t="s" s="5">
+      <c r="C54" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D54" s="7">
+        <v>570</v>
+      </c>
+      <c r="E54" t="s" s="6">
         <v>165</v>
       </c>
-      <c r="F54" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6">
+      <c r="F54" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G54" s="7">
         <v>28.7394069431122</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="7">
         <v>-106.118283236885</v>
       </c>
+      <c r="I54" s="8"/>
     </row>
     <row r="55" ht="13.55" customHeight="1">
-      <c r="A55" t="s" s="5">
+      <c r="A55" t="s" s="6">
         <v>166</v>
       </c>
-      <c r="B55" t="s" s="5">
+      <c r="B55" t="s" s="6">
         <v>167</v>
       </c>
-      <c r="C55" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D55" s="6">
-        <v>570</v>
-      </c>
-      <c r="E55" t="s" s="5">
+      <c r="C55" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D55" s="7">
+        <v>570</v>
+      </c>
+      <c r="E55" t="s" s="6">
         <v>168</v>
       </c>
-      <c r="F55" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G55" s="6">
+      <c r="F55" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G55" s="7">
         <v>28.7242945085432</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="7">
         <v>-106.126249144360</v>
       </c>
+      <c r="I55" s="8"/>
     </row>
     <row r="56" ht="13.55" customHeight="1">
-      <c r="A56" t="s" s="5">
+      <c r="A56" t="s" s="6">
         <v>169</v>
       </c>
-      <c r="B56" t="s" s="5">
+      <c r="B56" t="s" s="6">
         <v>170</v>
       </c>
-      <c r="C56" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D56" s="6">
-        <v>570</v>
-      </c>
-      <c r="E56" t="s" s="5">
+      <c r="C56" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D56" s="7">
+        <v>570</v>
+      </c>
+      <c r="E56" t="s" s="6">
         <v>171</v>
       </c>
-      <c r="F56" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G56" s="6">
+      <c r="F56" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7">
         <v>28.6519625386112</v>
       </c>
-      <c r="H56" s="6">
+      <c r="H56" s="7">
         <v>-106.031139032188</v>
       </c>
+      <c r="I56" s="8"/>
     </row>
     <row r="57" ht="13.55" customHeight="1">
-      <c r="A57" t="s" s="5">
+      <c r="A57" t="s" s="6">
         <v>172</v>
       </c>
-      <c r="B57" t="s" s="5">
+      <c r="B57" t="s" s="6">
         <v>173</v>
       </c>
-      <c r="C57" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D57" s="6">
-        <v>570</v>
-      </c>
-      <c r="E57" t="s" s="5">
+      <c r="C57" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D57" s="7">
+        <v>570</v>
+      </c>
+      <c r="E57" t="s" s="6">
         <v>174</v>
       </c>
-      <c r="F57" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
+      <c r="F57" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
     </row>
     <row r="58" ht="13.55" customHeight="1">
-      <c r="A58" t="s" s="5">
+      <c r="A58" t="s" s="6">
         <v>175</v>
       </c>
-      <c r="B58" t="s" s="5">
+      <c r="B58" t="s" s="6">
         <v>176</v>
       </c>
-      <c r="C58" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D58" s="6">
-        <v>570</v>
-      </c>
-      <c r="E58" t="s" s="5">
+      <c r="C58" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D58" s="7">
+        <v>570</v>
+      </c>
+      <c r="E58" t="s" s="6">
         <v>177</v>
       </c>
-      <c r="F58" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6">
+      <c r="F58" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G58" s="7">
         <v>28.7440583170112</v>
       </c>
-      <c r="H58" s="6">
+      <c r="H58" s="7">
         <v>-105.983282134091</v>
       </c>
+      <c r="I58" s="8"/>
     </row>
     <row r="59" ht="13.55" customHeight="1">
-      <c r="A59" t="s" s="5">
+      <c r="A59" t="s" s="6">
         <v>178</v>
       </c>
-      <c r="B59" t="s" s="5">
+      <c r="B59" t="s" s="6">
         <v>179</v>
       </c>
-      <c r="C59" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D59" s="6">
-        <v>570</v>
-      </c>
-      <c r="E59" t="s" s="5">
+      <c r="C59" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D59" s="7">
+        <v>570</v>
+      </c>
+      <c r="E59" t="s" s="6">
         <v>180</v>
       </c>
-      <c r="F59" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G59" s="6">
+      <c r="F59" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G59" s="7">
         <v>28.5902618673731</v>
       </c>
-      <c r="H59" s="6">
+      <c r="H59" s="7">
         <v>-106.110950667694</v>
       </c>
+      <c r="I59" s="8"/>
     </row>
     <row r="60" ht="13.55" customHeight="1">
-      <c r="A60" t="s" s="5">
+      <c r="A60" t="s" s="6">
         <v>181</v>
       </c>
-      <c r="B60" t="s" s="5">
+      <c r="B60" t="s" s="6">
         <v>182</v>
       </c>
-      <c r="C60" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D60" s="6">
-        <v>570</v>
-      </c>
-      <c r="E60" t="s" s="5">
+      <c r="C60" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D60" s="7">
+        <v>570</v>
+      </c>
+      <c r="E60" t="s" s="6">
         <v>183</v>
       </c>
-      <c r="F60" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G60" s="6">
+      <c r="F60" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G60" s="7">
         <v>28.663374263803</v>
       </c>
-      <c r="H60" s="6">
+      <c r="H60" s="7">
         <v>-106.109841206255</v>
       </c>
+      <c r="I60" s="8"/>
     </row>
     <row r="61" ht="13.55" customHeight="1">
-      <c r="A61" t="s" s="5">
+      <c r="A61" t="s" s="6">
         <v>184</v>
       </c>
-      <c r="B61" t="s" s="5">
+      <c r="B61" t="s" s="6">
         <v>185</v>
       </c>
-      <c r="C61" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D61" s="6">
-        <v>570</v>
-      </c>
-      <c r="E61" t="s" s="5">
+      <c r="C61" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D61" s="7">
+        <v>570</v>
+      </c>
+      <c r="E61" t="s" s="6">
         <v>186</v>
       </c>
-      <c r="F61" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G61" s="6">
+      <c r="F61" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G61" s="7">
         <v>28.7212656829315</v>
       </c>
-      <c r="H61" s="6">
+      <c r="H61" s="7">
         <v>-106.094147361996</v>
       </c>
+      <c r="I61" s="8"/>
     </row>
     <row r="62" ht="13.55" customHeight="1">
-      <c r="A62" t="s" s="5">
+      <c r="A62" t="s" s="6">
         <v>187</v>
       </c>
-      <c r="B62" t="s" s="5">
+      <c r="B62" t="s" s="6">
         <v>188</v>
       </c>
-      <c r="C62" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D62" s="6">
-        <v>570</v>
-      </c>
-      <c r="E62" t="s" s="5">
+      <c r="C62" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D62" s="7">
+        <v>570</v>
+      </c>
+      <c r="E62" t="s" s="6">
         <v>189</v>
       </c>
-      <c r="F62" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G62" s="6">
+      <c r="F62" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G62" s="7">
         <v>28.6090031861345</v>
       </c>
-      <c r="H62" s="6">
+      <c r="H62" s="7">
         <v>-106.017293426472</v>
       </c>
+      <c r="I62" s="8"/>
     </row>
     <row r="63" ht="13.55" customHeight="1">
-      <c r="A63" t="s" s="5">
+      <c r="A63" t="s" s="6">
         <v>190</v>
       </c>
-      <c r="B63" t="s" s="5">
+      <c r="B63" t="s" s="6">
         <v>191</v>
       </c>
-      <c r="C63" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D63" s="6">
-        <v>570</v>
-      </c>
-      <c r="E63" t="s" s="5">
+      <c r="C63" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D63" s="7">
+        <v>570</v>
+      </c>
+      <c r="E63" t="s" s="6">
         <v>192</v>
       </c>
-      <c r="F63" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G63" s="6">
+      <c r="F63" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G63" s="7">
         <v>28.6026522092612</v>
       </c>
-      <c r="H63" s="6">
+      <c r="H63" s="7">
         <v>-106.026947614168</v>
       </c>
+      <c r="I63" s="8"/>
     </row>
     <row r="64" ht="13.55" customHeight="1">
-      <c r="A64" t="s" s="5">
+      <c r="A64" t="s" s="6">
         <v>193</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="9">
         <v>41972</v>
       </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" t="s" s="5">
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" t="s" s="6">
         <v>194</v>
       </c>
-      <c r="F64" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G64" s="6">
+      <c r="F64" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G64" s="7">
         <v>28.5969514434161</v>
       </c>
-      <c r="H64" s="6">
+      <c r="H64" s="7">
         <v>-105.935932313539</v>
       </c>
+      <c r="I64" s="8"/>
     </row>
     <row r="65" ht="13.55" customHeight="1">
-      <c r="A65" t="s" s="5">
+      <c r="A65" t="s" s="6">
         <v>195</v>
       </c>
-      <c r="B65" t="s" s="5">
+      <c r="B65" t="s" s="6">
         <v>196</v>
       </c>
-      <c r="C65" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D65" s="6">
-        <v>570</v>
-      </c>
-      <c r="E65" t="s" s="5">
+      <c r="C65" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D65" s="7">
+        <v>570</v>
+      </c>
+      <c r="E65" t="s" s="6">
         <v>197</v>
       </c>
-      <c r="F65" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G65" s="6">
+      <c r="F65" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G65" s="7">
         <v>28.6174656592421</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H65" s="7">
         <v>-106.080741391544</v>
       </c>
+      <c r="I65" s="8"/>
     </row>
     <row r="66" ht="13.55" customHeight="1">
-      <c r="A66" t="s" s="5">
+      <c r="A66" t="s" s="6">
         <v>198</v>
       </c>
-      <c r="B66" t="s" s="5">
+      <c r="B66" t="s" s="6">
         <v>199</v>
       </c>
-      <c r="C66" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D66" s="6">
-        <v>570</v>
-      </c>
-      <c r="E66" t="s" s="5">
+      <c r="C66" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D66" s="7">
+        <v>570</v>
+      </c>
+      <c r="E66" t="s" s="6">
         <v>200</v>
       </c>
-      <c r="F66" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G66" s="6">
+      <c r="F66" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G66" s="7">
         <v>28.6414196661652</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="7">
         <v>-106.070715203781</v>
       </c>
+      <c r="I66" s="8"/>
     </row>
     <row r="67" ht="13.55" customHeight="1">
-      <c r="A67" t="s" s="5">
+      <c r="A67" t="s" s="6">
         <v>201</v>
       </c>
-      <c r="B67" t="s" s="5">
+      <c r="B67" t="s" s="6">
         <v>202</v>
       </c>
-      <c r="C67" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D67" s="6">
-        <v>570</v>
-      </c>
-      <c r="E67" t="s" s="5">
+      <c r="C67" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D67" s="7">
+        <v>570</v>
+      </c>
+      <c r="E67" t="s" s="6">
         <v>203</v>
       </c>
-      <c r="F67" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G67" s="6">
+      <c r="F67" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G67" s="7">
         <v>28.6197969084218</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H67" s="7">
         <v>-106.026244945337</v>
       </c>
+      <c r="I67" s="8"/>
     </row>
     <row r="68" ht="13.55" customHeight="1">
-      <c r="A68" t="s" s="5">
+      <c r="A68" t="s" s="6">
         <v>204</v>
       </c>
-      <c r="B68" t="s" s="5">
+      <c r="B68" t="s" s="6">
         <v>205</v>
       </c>
-      <c r="C68" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D68" s="6">
-        <v>570</v>
-      </c>
-      <c r="E68" t="s" s="5">
+      <c r="C68" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D68" s="7">
+        <v>570</v>
+      </c>
+      <c r="E68" t="s" s="6">
         <v>206</v>
       </c>
-      <c r="F68" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G68" s="6">
+      <c r="F68" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G68" s="7">
         <v>28.6503724986984</v>
       </c>
-      <c r="H68" s="6">
+      <c r="H68" s="7">
         <v>-106.091764340865</v>
       </c>
+      <c r="I68" s="8"/>
     </row>
     <row r="69" ht="13.55" customHeight="1">
-      <c r="A69" t="s" s="5">
+      <c r="A69" t="s" s="6">
         <v>207</v>
       </c>
-      <c r="B69" t="s" s="5">
+      <c r="B69" t="s" s="6">
         <v>208</v>
       </c>
-      <c r="C69" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D69" s="6">
-        <v>570</v>
-      </c>
-      <c r="E69" t="s" s="5">
+      <c r="C69" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D69" s="7">
+        <v>570</v>
+      </c>
+      <c r="E69" t="s" s="6">
         <v>209</v>
       </c>
-      <c r="F69" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G69" s="6">
+      <c r="F69" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G69" s="7">
         <v>28.6726315046401</v>
       </c>
-      <c r="H69" s="6">
+      <c r="H69" s="7">
         <v>-106.010584776864</v>
       </c>
+      <c r="I69" s="8"/>
     </row>
     <row r="70" ht="13.55" customHeight="1">
-      <c r="A70" t="s" s="5">
+      <c r="A70" t="s" s="6">
         <v>210</v>
       </c>
-      <c r="B70" t="s" s="5">
+      <c r="B70" t="s" s="6">
         <v>211</v>
       </c>
-      <c r="C70" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D70" s="6">
-        <v>570</v>
-      </c>
-      <c r="E70" t="s" s="5">
+      <c r="C70" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D70" s="7">
+        <v>570</v>
+      </c>
+      <c r="E70" t="s" s="6">
         <v>212</v>
       </c>
-      <c r="F70" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G70" s="6">
+      <c r="F70" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G70" s="7">
         <v>28.6489385441352</v>
       </c>
-      <c r="H70" s="6">
+      <c r="H70" s="7">
         <v>-106.076649591906</v>
       </c>
+      <c r="I70" s="8"/>
     </row>
     <row r="71" ht="13.55" customHeight="1">
-      <c r="A71" t="s" s="5">
+      <c r="A71" t="s" s="6">
         <v>213</v>
       </c>
-      <c r="B71" t="s" s="5">
+      <c r="B71" t="s" s="6">
         <v>214</v>
       </c>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" t="s" s="5">
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" t="s" s="6">
         <v>215</v>
       </c>
-      <c r="F71" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G71" s="6">
+      <c r="F71" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G71" s="7">
         <v>28.7099286262549</v>
       </c>
-      <c r="H71" s="6">
+      <c r="H71" s="7">
         <v>-106.083208183938</v>
       </c>
+      <c r="I71" s="8"/>
     </row>
     <row r="72" ht="13.55" customHeight="1">
-      <c r="A72" t="s" s="5">
+      <c r="A72" t="s" s="6">
         <v>216</v>
       </c>
-      <c r="B72" t="s" s="5">
+      <c r="B72" t="s" s="6">
         <v>217</v>
       </c>
-      <c r="C72" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D72" s="6">
-        <v>570</v>
-      </c>
-      <c r="E72" t="s" s="5">
+      <c r="C72" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D72" s="7">
+        <v>570</v>
+      </c>
+      <c r="E72" t="s" s="6">
         <v>218</v>
       </c>
-      <c r="F72" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G72" s="6">
+      <c r="F72" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G72" s="7">
         <v>28.618225323478</v>
       </c>
-      <c r="H72" s="6">
+      <c r="H72" s="7">
         <v>-106.092600699881</v>
       </c>
+      <c r="I72" s="8"/>
     </row>
     <row r="73" ht="13.55" customHeight="1">
-      <c r="A73" t="s" s="5">
+      <c r="A73" t="s" s="6">
         <v>219</v>
       </c>
-      <c r="B73" t="s" s="5">
+      <c r="B73" t="s" s="6">
         <v>220</v>
       </c>
-      <c r="C73" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D73" s="6">
-        <v>570</v>
-      </c>
-      <c r="E73" t="s" s="5">
+      <c r="C73" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D73" s="7">
+        <v>570</v>
+      </c>
+      <c r="E73" t="s" s="6">
         <v>221</v>
       </c>
-      <c r="F73" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G73" s="6">
+      <c r="F73" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G73" s="7">
         <v>28.6569976790632</v>
       </c>
-      <c r="H73" s="6">
+      <c r="H73" s="7">
         <v>-106.117079975432</v>
       </c>
+      <c r="I73" s="8"/>
     </row>
     <row r="74" ht="13.55" customHeight="1">
-      <c r="A74" t="s" s="5">
+      <c r="A74" t="s" s="6">
         <v>222</v>
       </c>
-      <c r="B74" t="s" s="5">
+      <c r="B74" t="s" s="6">
         <v>223</v>
       </c>
-      <c r="C74" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D74" s="6">
-        <v>570</v>
-      </c>
-      <c r="E74" t="s" s="5">
+      <c r="C74" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D74" s="7">
+        <v>570</v>
+      </c>
+      <c r="E74" t="s" s="6">
         <v>224</v>
       </c>
-      <c r="F74" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G74" s="6">
+      <c r="F74" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G74" s="7">
         <v>28.6371814871324</v>
       </c>
-      <c r="H74" s="6">
+      <c r="H74" s="7">
         <v>-106.122265635769</v>
       </c>
+      <c r="I74" s="8"/>
     </row>
     <row r="75" ht="13.55" customHeight="1">
-      <c r="A75" t="s" s="5">
+      <c r="A75" t="s" s="6">
         <v>225</v>
       </c>
-      <c r="B75" t="s" s="5">
+      <c r="B75" t="s" s="6">
         <v>226</v>
       </c>
-      <c r="C75" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D75" s="6">
-        <v>570</v>
-      </c>
-      <c r="E75" t="s" s="5">
+      <c r="C75" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D75" s="7">
+        <v>570</v>
+      </c>
+      <c r="E75" t="s" s="6">
         <v>227</v>
       </c>
-      <c r="F75" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G75" s="6">
+      <c r="F75" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G75" s="7">
         <v>28.679410467184</v>
       </c>
-      <c r="H75" s="6">
+      <c r="H75" s="7">
         <v>-106.089100313585</v>
       </c>
+      <c r="I75" s="8"/>
     </row>
     <row r="76" ht="13.55" customHeight="1">
-      <c r="A76" t="s" s="5">
+      <c r="A76" t="s" s="6">
         <v>228</v>
       </c>
-      <c r="B76" t="s" s="5">
+      <c r="B76" t="s" s="6">
         <v>229</v>
       </c>
-      <c r="C76" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D76" s="6">
-        <v>570</v>
-      </c>
-      <c r="E76" t="s" s="5">
+      <c r="C76" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D76" s="7">
+        <v>570</v>
+      </c>
+      <c r="E76" t="s" s="6">
         <v>230</v>
       </c>
-      <c r="F76" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G76" s="6">
+      <c r="F76" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G76" s="7">
         <v>28.6622620095507</v>
       </c>
-      <c r="H76" s="6">
+      <c r="H76" s="7">
         <v>-106.120982129666</v>
       </c>
+      <c r="I76" s="8"/>
     </row>
     <row r="77" ht="13.55" customHeight="1">
-      <c r="A77" t="s" s="5">
+      <c r="A77" t="s" s="6">
         <v>231</v>
       </c>
-      <c r="B77" t="s" s="5">
+      <c r="B77" t="s" s="6">
         <v>232</v>
       </c>
-      <c r="C77" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D77" s="6">
-        <v>570</v>
-      </c>
-      <c r="E77" t="s" s="5">
+      <c r="C77" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D77" s="7">
+        <v>570</v>
+      </c>
+      <c r="E77" t="s" s="6">
         <v>233</v>
       </c>
-      <c r="F77" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G77" s="6">
+      <c r="F77" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G77" s="7">
         <v>28.6669144733998</v>
       </c>
-      <c r="H77" s="6">
+      <c r="H77" s="7">
         <v>-106.111353331896</v>
       </c>
+      <c r="I77" s="8"/>
     </row>
     <row r="78" ht="13.55" customHeight="1">
-      <c r="A78" t="s" s="5">
+      <c r="A78" t="s" s="6">
         <v>234</v>
       </c>
-      <c r="B78" t="s" s="5">
+      <c r="B78" t="s" s="6">
         <v>235</v>
       </c>
-      <c r="C78" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D78" s="6">
-        <v>570</v>
-      </c>
-      <c r="E78" t="s" s="5">
+      <c r="C78" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D78" s="7">
+        <v>570</v>
+      </c>
+      <c r="E78" t="s" s="6">
         <v>236</v>
       </c>
-      <c r="F78" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G78" s="6">
+      <c r="F78" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G78" s="7">
         <v>28.6554593198336</v>
       </c>
-      <c r="H78" s="6">
+      <c r="H78" s="7">
         <v>-105.963831496466</v>
       </c>
+      <c r="I78" s="8"/>
     </row>
     <row r="79" ht="13.55" customHeight="1">
-      <c r="A79" t="s" s="5">
+      <c r="A79" t="s" s="6">
         <v>237</v>
       </c>
-      <c r="B79" t="s" s="5">
+      <c r="B79" t="s" s="6">
         <v>238</v>
       </c>
-      <c r="C79" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D79" s="6">
-        <v>570</v>
-      </c>
-      <c r="E79" t="s" s="5">
+      <c r="C79" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D79" s="7">
+        <v>570</v>
+      </c>
+      <c r="E79" t="s" s="6">
         <v>239</v>
       </c>
-      <c r="F79" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G79" s="6">
+      <c r="F79" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G79" s="7">
         <v>28.7504063516263</v>
       </c>
-      <c r="H79" s="6">
+      <c r="H79" s="7">
         <v>-106.131442302131</v>
       </c>
+      <c r="I79" s="8"/>
     </row>
     <row r="80" ht="13.55" customHeight="1">
-      <c r="A80" t="s" s="5">
+      <c r="A80" t="s" s="6">
         <v>240</v>
       </c>
-      <c r="B80" t="s" s="5">
+      <c r="B80" t="s" s="6">
         <v>241</v>
       </c>
-      <c r="C80" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D80" s="6">
-        <v>570</v>
-      </c>
-      <c r="E80" t="s" s="5">
+      <c r="C80" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D80" s="7">
+        <v>570</v>
+      </c>
+      <c r="E80" t="s" s="6">
         <v>242</v>
       </c>
-      <c r="F80" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G80" s="6">
+      <c r="F80" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7">
         <v>28.6280429305957</v>
       </c>
-      <c r="H80" s="6">
+      <c r="H80" s="7">
         <v>-106.062487543536</v>
       </c>
+      <c r="I80" s="8"/>
     </row>
     <row r="81" ht="13.55" customHeight="1">
-      <c r="A81" t="s" s="5">
+      <c r="A81" t="s" s="6">
         <v>243</v>
       </c>
-      <c r="B81" t="s" s="5">
+      <c r="B81" t="s" s="6">
         <v>244</v>
       </c>
-      <c r="C81" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D81" s="6">
-        <v>570</v>
-      </c>
-      <c r="E81" t="s" s="5">
+      <c r="C81" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D81" s="7">
+        <v>570</v>
+      </c>
+      <c r="E81" t="s" s="6">
         <v>245</v>
       </c>
-      <c r="F81" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G81" s="6">
+      <c r="F81" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G81" s="7">
         <v>28.6602104677595</v>
       </c>
-      <c r="H81" s="6">
+      <c r="H81" s="7">
         <v>-106.072326811726</v>
       </c>
+      <c r="I81" s="8"/>
     </row>
     <row r="82" ht="13.55" customHeight="1">
-      <c r="A82" t="s" s="5">
+      <c r="A82" t="s" s="6">
         <v>246</v>
       </c>
-      <c r="B82" t="s" s="5">
+      <c r="B82" t="s" s="6">
         <v>247</v>
       </c>
-      <c r="C82" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D82" s="6">
-        <v>570</v>
-      </c>
-      <c r="E82" t="s" s="5">
+      <c r="C82" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D82" s="7">
+        <v>570</v>
+      </c>
+      <c r="E82" t="s" s="6">
         <v>248</v>
       </c>
-      <c r="F82" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G82" s="6">
+      <c r="F82" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G82" s="7">
         <v>28.6802978913798</v>
       </c>
-      <c r="H82" s="6">
+      <c r="H82" s="7">
         <v>-106.121068705223</v>
       </c>
+      <c r="I82" s="8"/>
     </row>
     <row r="83" ht="13.55" customHeight="1">
-      <c r="A83" t="s" s="5">
+      <c r="A83" t="s" s="6">
         <v>249</v>
       </c>
-      <c r="B83" t="s" s="5">
+      <c r="B83" t="s" s="6">
         <v>250</v>
       </c>
-      <c r="C83" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D83" s="6">
-        <v>570</v>
-      </c>
-      <c r="E83" t="s" s="5">
+      <c r="C83" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D83" s="7">
+        <v>570</v>
+      </c>
+      <c r="E83" t="s" s="6">
         <v>251</v>
       </c>
-      <c r="F83" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G83" s="6">
+      <c r="F83" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G83" s="7">
         <v>28.6530404514821</v>
       </c>
-      <c r="H83" s="6">
+      <c r="H83" s="7">
         <v>-106.097956534985</v>
       </c>
+      <c r="I83" s="8"/>
     </row>
     <row r="84" ht="13.55" customHeight="1">
-      <c r="A84" t="s" s="5">
+      <c r="A84" t="s" s="6">
         <v>252</v>
       </c>
-      <c r="B84" t="s" s="5">
+      <c r="B84" t="s" s="6">
         <v>253</v>
       </c>
-      <c r="C84" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D84" s="6">
-        <v>570</v>
-      </c>
-      <c r="E84" t="s" s="5">
+      <c r="C84" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D84" s="7">
+        <v>570</v>
+      </c>
+      <c r="E84" t="s" s="6">
         <v>254</v>
       </c>
-      <c r="F84" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G84" s="6">
+      <c r="F84" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G84" s="7">
         <v>28.6725083315547</v>
       </c>
-      <c r="H84" s="6">
+      <c r="H84" s="7">
         <v>-106.078688579573</v>
       </c>
+      <c r="I84" s="8"/>
     </row>
     <row r="85" ht="13.55" customHeight="1">
-      <c r="A85" t="s" s="5">
+      <c r="A85" t="s" s="6">
         <v>255</v>
       </c>
-      <c r="B85" t="s" s="5">
+      <c r="B85" t="s" s="6">
         <v>256</v>
       </c>
-      <c r="C85" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D85" s="6">
-        <v>570</v>
-      </c>
-      <c r="E85" t="s" s="5">
+      <c r="C85" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D85" s="7">
+        <v>570</v>
+      </c>
+      <c r="E85" t="s" s="6">
         <v>257</v>
       </c>
-      <c r="F85" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G85" s="6">
+      <c r="F85" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G85" s="7">
         <v>28.5904465446645</v>
       </c>
-      <c r="H85" s="6">
+      <c r="H85" s="7">
         <v>-106.153022263721</v>
       </c>
+      <c r="I85" s="8"/>
     </row>
     <row r="86" ht="13.55" customHeight="1">
-      <c r="A86" t="s" s="5">
+      <c r="A86" t="s" s="6">
         <v>258</v>
       </c>
-      <c r="B86" t="s" s="5">
+      <c r="B86" t="s" s="6">
         <v>259</v>
       </c>
-      <c r="C86" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D86" s="6">
-        <v>570</v>
-      </c>
-      <c r="E86" t="s" s="5">
+      <c r="C86" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D86" s="7">
+        <v>570</v>
+      </c>
+      <c r="E86" t="s" s="6">
         <v>260</v>
       </c>
-      <c r="F86" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G86" s="6">
+      <c r="F86" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G86" s="7">
         <v>28.6880917867181</v>
       </c>
-      <c r="H86" s="6">
+      <c r="H86" s="7">
         <v>-106.097743244879</v>
       </c>
+      <c r="I86" s="8"/>
     </row>
     <row r="87" ht="13.55" customHeight="1">
-      <c r="A87" t="s" s="5">
+      <c r="A87" t="s" s="6">
         <v>261</v>
       </c>
-      <c r="B87" t="s" s="5">
+      <c r="B87" t="s" s="6">
         <v>262</v>
       </c>
-      <c r="C87" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D87" s="6">
-        <v>570</v>
-      </c>
-      <c r="E87" t="s" s="5">
+      <c r="C87" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D87" s="7">
+        <v>570</v>
+      </c>
+      <c r="E87" t="s" s="6">
         <v>263</v>
       </c>
-      <c r="F87" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G87" s="6">
+      <c r="F87" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G87" s="7">
         <v>28.6665047488011</v>
       </c>
-      <c r="H87" s="6">
+      <c r="H87" s="7">
         <v>-105.984323669901</v>
       </c>
+      <c r="I87" s="8"/>
     </row>
     <row r="88" ht="13.55" customHeight="1">
-      <c r="A88" t="s" s="5">
+      <c r="A88" t="s" s="6">
         <v>264</v>
       </c>
-      <c r="B88" t="s" s="5">
+      <c r="B88" t="s" s="6">
         <v>265</v>
       </c>
-      <c r="C88" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D88" s="6">
-        <v>570</v>
-      </c>
-      <c r="E88" t="s" s="5">
+      <c r="C88" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D88" s="7">
+        <v>570</v>
+      </c>
+      <c r="E88" t="s" s="6">
         <v>266</v>
       </c>
-      <c r="F88" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G88" s="6">
+      <c r="F88" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G88" s="7">
         <v>28.5957231175784</v>
       </c>
-      <c r="H88" s="6">
+      <c r="H88" s="7">
         <v>-106.012141620155</v>
       </c>
+      <c r="I88" s="8"/>
     </row>
     <row r="89" ht="13.55" customHeight="1">
-      <c r="A89" t="s" s="5">
+      <c r="A89" t="s" s="6">
         <v>267</v>
       </c>
-      <c r="B89" t="s" s="5">
+      <c r="B89" t="s" s="6">
         <v>268</v>
       </c>
-      <c r="C89" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D89" s="6">
-        <v>570</v>
-      </c>
-      <c r="E89" t="s" s="5">
+      <c r="C89" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D89" s="7">
+        <v>570</v>
+      </c>
+      <c r="E89" t="s" s="6">
         <v>269</v>
       </c>
-      <c r="F89" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G89" s="6">
+      <c r="F89" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G89" s="7">
         <v>28.6950150076868</v>
       </c>
-      <c r="H89" s="6">
+      <c r="H89" s="7">
         <v>-106.116500555901</v>
       </c>
+      <c r="I89" s="8"/>
     </row>
     <row r="90" ht="13.55" customHeight="1">
-      <c r="A90" t="s" s="5">
+      <c r="A90" t="s" s="6">
         <v>270</v>
       </c>
-      <c r="B90" t="s" s="5">
+      <c r="B90" t="s" s="6">
         <v>271</v>
       </c>
-      <c r="C90" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D90" s="6">
-        <v>570</v>
-      </c>
-      <c r="E90" t="s" s="5">
+      <c r="C90" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D90" s="7">
+        <v>570</v>
+      </c>
+      <c r="E90" t="s" s="6">
         <v>272</v>
       </c>
-      <c r="F90" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G90" s="6">
+      <c r="F90" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G90" s="7">
         <v>28.6830928358021</v>
       </c>
-      <c r="H90" s="6">
+      <c r="H90" s="7">
         <v>-106.101065007531</v>
       </c>
+      <c r="I90" s="8"/>
     </row>
     <row r="91" ht="13.55" customHeight="1">
-      <c r="A91" t="s" s="5">
+      <c r="A91" t="s" s="6">
         <v>273</v>
       </c>
-      <c r="B91" t="s" s="5">
+      <c r="B91" t="s" s="6">
         <v>274</v>
       </c>
-      <c r="C91" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D91" s="6">
-        <v>570</v>
-      </c>
-      <c r="E91" t="s" s="5">
+      <c r="C91" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D91" s="7">
+        <v>570</v>
+      </c>
+      <c r="E91" t="s" s="6">
         <v>275</v>
       </c>
-      <c r="F91" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G91" s="6">
+      <c r="F91" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G91" s="7">
         <v>28.6450880733833</v>
       </c>
-      <c r="H91" s="6">
+      <c r="H91" s="7">
         <v>-106.014714900995</v>
       </c>
+      <c r="I91" s="8"/>
     </row>
     <row r="92" ht="13.55" customHeight="1">
-      <c r="A92" t="s" s="5">
+      <c r="A92" t="s" s="6">
         <v>276</v>
       </c>
-      <c r="B92" t="s" s="5">
+      <c r="B92" t="s" s="6">
         <v>277</v>
       </c>
-      <c r="C92" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D92" s="6">
-        <v>570</v>
-      </c>
-      <c r="E92" t="s" s="5">
+      <c r="C92" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D92" s="7">
+        <v>570</v>
+      </c>
+      <c r="E92" t="s" s="6">
         <v>278</v>
       </c>
-      <c r="F92" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G92" s="6">
+      <c r="F92" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G92" s="7">
         <v>28.653535143682</v>
       </c>
-      <c r="H92" s="6">
+      <c r="H92" s="7">
         <v>-106.060695998396</v>
       </c>
+      <c r="I92" s="8"/>
     </row>
     <row r="93" ht="13.55" customHeight="1">
-      <c r="A93" t="s" s="5">
+      <c r="A93" t="s" s="6">
         <v>279</v>
       </c>
-      <c r="B93" t="s" s="5">
+      <c r="B93" t="s" s="6">
         <v>280</v>
       </c>
-      <c r="C93" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D93" s="6">
-        <v>570</v>
-      </c>
-      <c r="E93" t="s" s="5">
+      <c r="C93" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D93" s="7">
+        <v>570</v>
+      </c>
+      <c r="E93" t="s" s="6">
         <v>281</v>
       </c>
-      <c r="F93" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G93" s="6">
+      <c r="F93" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G93" s="7">
         <v>28.6980519213653</v>
       </c>
-      <c r="H93" s="6">
+      <c r="H93" s="7">
         <v>-106.131055383958</v>
       </c>
+      <c r="I93" s="8"/>
     </row>
     <row r="94" ht="13.55" customHeight="1">
-      <c r="A94" t="s" s="5">
+      <c r="A94" t="s" s="6">
         <v>282</v>
       </c>
-      <c r="B94" t="s" s="5">
+      <c r="B94" t="s" s="6">
         <v>283</v>
       </c>
-      <c r="C94" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D94" s="6">
-        <v>570</v>
-      </c>
-      <c r="E94" t="s" s="5">
+      <c r="C94" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D94" s="7">
+        <v>570</v>
+      </c>
+      <c r="E94" t="s" s="6">
         <v>284</v>
       </c>
-      <c r="F94" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G94" s="6">
+      <c r="F94" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G94" s="7">
         <v>28.6784669111351</v>
       </c>
-      <c r="H94" s="6">
+      <c r="H94" s="7">
         <v>-106.105227059211</v>
       </c>
+      <c r="I94" s="8"/>
     </row>
     <row r="95" ht="13.55" customHeight="1">
-      <c r="A95" t="s" s="5">
+      <c r="A95" t="s" s="6">
         <v>285</v>
       </c>
-      <c r="B95" t="s" s="5">
+      <c r="B95" t="s" s="6">
         <v>286</v>
       </c>
-      <c r="C95" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D95" s="6">
-        <v>570</v>
-      </c>
-      <c r="E95" t="s" s="5">
+      <c r="C95" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D95" s="7">
+        <v>570</v>
+      </c>
+      <c r="E95" t="s" s="6">
         <v>287</v>
       </c>
-      <c r="F95" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G95" s="6">
+      <c r="F95" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G95" s="7">
         <v>28.6030326454364</v>
       </c>
-      <c r="H95" s="6">
+      <c r="H95" s="7">
         <v>-106.018950897795</v>
       </c>
+      <c r="I95" s="8"/>
     </row>
     <row r="96" ht="13.55" customHeight="1">
-      <c r="A96" t="s" s="5">
+      <c r="A96" t="s" s="6">
         <v>288</v>
       </c>
-      <c r="B96" t="s" s="5">
+      <c r="B96" t="s" s="6">
         <v>289</v>
       </c>
-      <c r="C96" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D96" s="6">
-        <v>570</v>
-      </c>
-      <c r="E96" t="s" s="5">
+      <c r="C96" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D96" s="7">
+        <v>570</v>
+      </c>
+      <c r="E96" t="s" s="6">
         <v>290</v>
       </c>
-      <c r="F96" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G96" s="6">
+      <c r="F96" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G96" s="7">
         <v>28.5839543555538</v>
       </c>
-      <c r="H96" s="6">
+      <c r="H96" s="7">
         <v>-105.959753138340</v>
       </c>
+      <c r="I96" s="8"/>
     </row>
     <row r="97" ht="13.55" customHeight="1">
-      <c r="A97" t="s" s="5">
+      <c r="A97" t="s" s="6">
         <v>291</v>
       </c>
-      <c r="B97" t="s" s="5">
+      <c r="B97" t="s" s="6">
         <v>292</v>
       </c>
-      <c r="C97" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D97" s="6">
-        <v>570</v>
-      </c>
-      <c r="E97" t="s" s="5">
+      <c r="C97" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D97" s="7">
+        <v>570</v>
+      </c>
+      <c r="E97" t="s" s="6">
         <v>293</v>
       </c>
-      <c r="F97" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G97" s="6">
+      <c r="F97" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G97" s="7">
         <v>28.6207971064462</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H97" s="7">
         <v>-106.033484641404</v>
       </c>
+      <c r="I97" s="8"/>
     </row>
     <row r="98" ht="13.55" customHeight="1">
-      <c r="A98" t="s" s="5">
+      <c r="A98" t="s" s="6">
         <v>294</v>
       </c>
-      <c r="B98" t="s" s="5">
+      <c r="B98" t="s" s="6">
         <v>295</v>
       </c>
-      <c r="C98" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D98" s="6">
-        <v>570</v>
-      </c>
-      <c r="E98" t="s" s="5">
+      <c r="C98" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D98" s="7">
+        <v>570</v>
+      </c>
+      <c r="E98" t="s" s="6">
         <v>296</v>
       </c>
-      <c r="F98" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G98" s="6">
+      <c r="F98" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G98" s="7">
         <v>28.6209091888674</v>
       </c>
-      <c r="H98" s="6">
+      <c r="H98" s="7">
         <v>-106.101700672461</v>
       </c>
+      <c r="I98" s="8"/>
     </row>
     <row r="99" ht="13.55" customHeight="1">
-      <c r="A99" t="s" s="5">
+      <c r="A99" t="s" s="6">
         <v>297</v>
       </c>
-      <c r="B99" t="s" s="5">
+      <c r="B99" t="s" s="6">
         <v>298</v>
       </c>
-      <c r="C99" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D99" s="6">
-        <v>570</v>
-      </c>
-      <c r="E99" t="s" s="5">
+      <c r="C99" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D99" s="7">
+        <v>570</v>
+      </c>
+      <c r="E99" t="s" s="6">
         <v>299</v>
       </c>
-      <c r="F99" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G99" s="6">
+      <c r="F99" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G99" s="7">
         <v>28.6648898767515</v>
       </c>
-      <c r="H99" s="6">
+      <c r="H99" s="7">
         <v>-106.002285145641</v>
       </c>
+      <c r="I99" s="8"/>
     </row>
     <row r="100" ht="13.55" customHeight="1">
-      <c r="A100" t="s" s="5">
+      <c r="A100" t="s" s="6">
         <v>300</v>
       </c>
-      <c r="B100" t="s" s="5">
+      <c r="B100" t="s" s="6">
         <v>301</v>
       </c>
-      <c r="C100" s="7"/>
-      <c r="D100" s="6">
-        <v>570</v>
-      </c>
-      <c r="E100" t="s" s="5">
+      <c r="C100" s="8"/>
+      <c r="D100" s="7">
+        <v>570</v>
+      </c>
+      <c r="E100" t="s" s="6">
         <v>302</v>
       </c>
-      <c r="F100" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G100" s="6">
+      <c r="F100" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G100" s="7">
         <v>28.6072205126151</v>
       </c>
-      <c r="H100" s="6">
+      <c r="H100" s="7">
         <v>-105.933247667660</v>
       </c>
+      <c r="I100" s="8"/>
     </row>
     <row r="101" ht="13.55" customHeight="1">
-      <c r="A101" t="s" s="5">
+      <c r="A101" t="s" s="6">
         <v>303</v>
       </c>
-      <c r="B101" t="s" s="5">
+      <c r="B101" t="s" s="6">
         <v>304</v>
       </c>
-      <c r="C101" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D101" s="6">
-        <v>570</v>
-      </c>
-      <c r="E101" t="s" s="5">
+      <c r="C101" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D101" s="7">
+        <v>570</v>
+      </c>
+      <c r="E101" t="s" s="6">
         <v>305</v>
       </c>
-      <c r="F101" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G101" s="6">
+      <c r="F101" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G101" s="7">
         <v>28.699591267650</v>
       </c>
-      <c r="H101" s="6">
+      <c r="H101" s="7">
         <v>-106.120584510529</v>
       </c>
+      <c r="I101" s="8"/>
     </row>
     <row r="102" ht="13.55" customHeight="1">
-      <c r="A102" t="s" s="5">
+      <c r="A102" t="s" s="6">
         <v>306</v>
       </c>
-      <c r="B102" t="s" s="5">
+      <c r="B102" t="s" s="6">
         <v>307</v>
       </c>
-      <c r="C102" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D102" s="6">
-        <v>570</v>
-      </c>
-      <c r="E102" t="s" s="5">
+      <c r="C102" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D102" s="7">
+        <v>570</v>
+      </c>
+      <c r="E102" t="s" s="6">
         <v>308</v>
       </c>
-      <c r="F102" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G102" s="6">
+      <c r="F102" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G102" s="7">
         <v>28.6607235561628</v>
       </c>
-      <c r="H102" s="6">
+      <c r="H102" s="7">
         <v>-106.112907953690</v>
       </c>
+      <c r="I102" s="8"/>
     </row>
     <row r="103" ht="13.55" customHeight="1">
-      <c r="A103" t="s" s="5">
+      <c r="A103" t="s" s="6">
         <v>309</v>
       </c>
-      <c r="B103" t="s" s="5">
+      <c r="B103" t="s" s="6">
         <v>310</v>
       </c>
-      <c r="C103" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D103" s="6">
-        <v>570</v>
-      </c>
-      <c r="E103" t="s" s="5">
+      <c r="C103" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D103" s="7">
+        <v>570</v>
+      </c>
+      <c r="E103" t="s" s="6">
         <v>311</v>
       </c>
-      <c r="F103" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G103" s="6">
+      <c r="F103" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G103" s="7">
         <v>28.6534413920254</v>
       </c>
-      <c r="H103" s="6">
+      <c r="H103" s="7">
         <v>-106.129924402223</v>
       </c>
+      <c r="I103" s="8"/>
     </row>
     <row r="104" ht="13.55" customHeight="1">
-      <c r="A104" t="s" s="5">
+      <c r="A104" t="s" s="6">
         <v>312</v>
       </c>
-      <c r="B104" t="s" s="5">
+      <c r="B104" t="s" s="6">
         <v>313</v>
       </c>
-      <c r="C104" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D104" s="6">
-        <v>570</v>
-      </c>
-      <c r="E104" t="s" s="5">
+      <c r="C104" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D104" s="7">
+        <v>570</v>
+      </c>
+      <c r="E104" t="s" s="6">
         <v>314</v>
       </c>
-      <c r="F104" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G104" s="6">
+      <c r="F104" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G104" s="7">
         <v>28.7322721531403</v>
       </c>
-      <c r="H104" s="6">
+      <c r="H104" s="7">
         <v>-106.116360494103</v>
       </c>
+      <c r="I104" s="8"/>
     </row>
     <row r="105" ht="13.55" customHeight="1">
-      <c r="A105" t="s" s="5">
+      <c r="A105" t="s" s="6">
         <v>315</v>
       </c>
-      <c r="B105" t="s" s="5">
+      <c r="B105" t="s" s="6">
         <v>316</v>
       </c>
-      <c r="C105" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D105" s="6">
-        <v>570</v>
-      </c>
-      <c r="E105" t="s" s="5">
+      <c r="C105" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D105" s="7">
+        <v>570</v>
+      </c>
+      <c r="E105" t="s" s="6">
         <v>317</v>
       </c>
-      <c r="F105" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G105" s="6">
+      <c r="F105" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G105" s="7">
         <v>28.6779410141631</v>
       </c>
-      <c r="H105" s="6">
+      <c r="H105" s="7">
         <v>-106.035615972503</v>
       </c>
+      <c r="I105" s="8"/>
     </row>
     <row r="106" ht="13.55" customHeight="1">
-      <c r="A106" t="s" s="5">
+      <c r="A106" t="s" s="6">
         <v>318</v>
       </c>
-      <c r="B106" t="s" s="5">
+      <c r="B106" t="s" s="6">
         <v>319</v>
       </c>
-      <c r="C106" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D106" s="6">
-        <v>570</v>
-      </c>
-      <c r="E106" t="s" s="5">
+      <c r="C106" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D106" s="7">
+        <v>570</v>
+      </c>
+      <c r="E106" t="s" s="6">
         <v>320</v>
       </c>
-      <c r="F106" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G106" s="6">
+      <c r="F106" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G106" s="7">
         <v>28.6280076693438</v>
       </c>
-      <c r="H106" s="6">
+      <c r="H106" s="7">
         <v>-106.073048025506</v>
       </c>
+      <c r="I106" s="8"/>
     </row>
     <row r="107" ht="13.55" customHeight="1">
-      <c r="A107" t="s" s="5">
+      <c r="A107" t="s" s="6">
         <v>321</v>
       </c>
-      <c r="B107" t="s" s="5">
+      <c r="B107" t="s" s="6">
         <v>322</v>
       </c>
-      <c r="C107" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D107" s="6">
-        <v>570</v>
-      </c>
-      <c r="E107" t="s" s="5">
+      <c r="C107" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D107" s="7">
+        <v>570</v>
+      </c>
+      <c r="E107" t="s" s="6">
         <v>323</v>
       </c>
-      <c r="F107" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G107" s="6">
+      <c r="F107" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G107" s="7">
         <v>28.6418827860075</v>
       </c>
-      <c r="H107" s="6">
+      <c r="H107" s="7">
         <v>-106.102472484616</v>
       </c>
+      <c r="I107" s="8"/>
     </row>
     <row r="108" ht="13.55" customHeight="1">
-      <c r="A108" t="s" s="5">
+      <c r="A108" t="s" s="6">
         <v>324</v>
       </c>
-      <c r="B108" t="s" s="5">
+      <c r="B108" t="s" s="6">
         <v>325</v>
       </c>
-      <c r="C108" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D108" s="6">
-        <v>570</v>
-      </c>
-      <c r="E108" t="s" s="5">
+      <c r="C108" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D108" s="7">
+        <v>570</v>
+      </c>
+      <c r="E108" t="s" s="6">
         <v>326</v>
       </c>
-      <c r="F108" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G108" s="6">
+      <c r="F108" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G108" s="7">
         <v>28.5858914183999</v>
       </c>
-      <c r="H108" s="6">
+      <c r="H108" s="7">
         <v>-106.114921637207</v>
       </c>
+      <c r="I108" s="8"/>
     </row>
     <row r="109" ht="13.55" customHeight="1">
-      <c r="A109" t="s" s="5">
+      <c r="A109" t="s" s="6">
         <v>327</v>
       </c>
-      <c r="B109" t="s" s="5">
+      <c r="B109" t="s" s="6">
         <v>328</v>
       </c>
-      <c r="C109" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D109" s="6">
-        <v>570</v>
-      </c>
-      <c r="E109" t="s" s="5">
+      <c r="C109" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D109" s="7">
+        <v>570</v>
+      </c>
+      <c r="E109" t="s" s="6">
         <v>329</v>
       </c>
-      <c r="F109" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G109" s="6">
+      <c r="F109" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G109" s="7">
         <v>28.7175812521216</v>
       </c>
-      <c r="H109" s="6">
+      <c r="H109" s="7">
         <v>-106.146982764445</v>
       </c>
+      <c r="I109" s="8"/>
     </row>
     <row r="110" ht="13.55" customHeight="1">
-      <c r="A110" t="s" s="5">
+      <c r="A110" t="s" s="6">
         <v>330</v>
       </c>
-      <c r="B110" t="s" s="5">
+      <c r="B110" t="s" s="6">
         <v>331</v>
       </c>
-      <c r="C110" s="7"/>
-      <c r="D110" s="6">
-        <v>570</v>
-      </c>
-      <c r="E110" t="s" s="5">
+      <c r="C110" s="8"/>
+      <c r="D110" s="7">
+        <v>570</v>
+      </c>
+      <c r="E110" t="s" s="6">
         <v>332</v>
       </c>
-      <c r="F110" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G110" s="6">
+      <c r="F110" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G110" s="7">
         <v>28.5969362719099</v>
       </c>
-      <c r="H110" s="6">
+      <c r="H110" s="7">
         <v>-106.018212652767</v>
       </c>
+      <c r="I110" s="8"/>
     </row>
     <row r="111" ht="13.55" customHeight="1">
-      <c r="A111" t="s" s="5">
+      <c r="A111" t="s" s="6">
         <v>333</v>
       </c>
-      <c r="B111" t="s" s="5">
+      <c r="B111" t="s" s="6">
         <v>334</v>
       </c>
-      <c r="C111" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D111" s="6">
-        <v>570</v>
-      </c>
-      <c r="E111" t="s" s="5">
+      <c r="C111" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D111" s="7">
+        <v>570</v>
+      </c>
+      <c r="E111" t="s" s="6">
         <v>335</v>
       </c>
-      <c r="F111" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G111" s="6">
+      <c r="F111" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G111" s="7">
         <v>28.735637560740</v>
       </c>
-      <c r="H111" s="6">
+      <c r="H111" s="7">
         <v>-106.136492605401</v>
       </c>
+      <c r="I111" s="8"/>
     </row>
     <row r="112" ht="13.55" customHeight="1">
-      <c r="A112" t="s" s="5">
+      <c r="A112" t="s" s="6">
         <v>336</v>
       </c>
-      <c r="B112" t="s" s="5">
+      <c r="B112" t="s" s="6">
         <v>337</v>
       </c>
-      <c r="C112" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D112" s="6">
-        <v>570</v>
-      </c>
-      <c r="E112" t="s" s="5">
+      <c r="C112" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D112" s="7">
+        <v>570</v>
+      </c>
+      <c r="E112" t="s" s="6">
         <v>338</v>
       </c>
-      <c r="F112" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G112" s="6">
+      <c r="F112" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G112" s="7">
         <v>28.6490371159752</v>
       </c>
-      <c r="H112" s="6">
+      <c r="H112" s="7">
         <v>-106.081551905717</v>
       </c>
+      <c r="I112" s="8"/>
     </row>
     <row r="113" ht="13.55" customHeight="1">
-      <c r="A113" t="s" s="5">
+      <c r="A113" t="s" s="6">
         <v>339</v>
       </c>
-      <c r="B113" t="s" s="5">
+      <c r="B113" t="s" s="6">
         <v>340</v>
       </c>
-      <c r="C113" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D113" s="6">
-        <v>570</v>
-      </c>
-      <c r="E113" t="s" s="5">
+      <c r="C113" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D113" s="7">
+        <v>570</v>
+      </c>
+      <c r="E113" t="s" s="6">
         <v>341</v>
       </c>
-      <c r="F113" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G113" s="6">
+      <c r="F113" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G113" s="7">
         <v>28.6771609213584</v>
       </c>
-      <c r="H113" s="6">
+      <c r="H113" s="7">
         <v>-106.126842384077</v>
       </c>
+      <c r="I113" s="8"/>
     </row>
     <row r="114" ht="13.55" customHeight="1">
-      <c r="A114" t="s" s="5">
+      <c r="A114" t="s" s="6">
         <v>342</v>
       </c>
-      <c r="B114" t="s" s="5">
+      <c r="B114" t="s" s="6">
         <v>343</v>
       </c>
-      <c r="C114" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D114" s="6">
-        <v>570</v>
-      </c>
-      <c r="E114" t="s" s="5">
+      <c r="C114" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D114" s="7">
+        <v>570</v>
+      </c>
+      <c r="E114" t="s" s="6">
         <v>344</v>
       </c>
-      <c r="F114" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G114" s="6">
+      <c r="F114" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G114" s="7">
         <v>28.6088641231822</v>
       </c>
-      <c r="H114" s="6">
+      <c r="H114" s="7">
         <v>-106.033271390778</v>
       </c>
+      <c r="I114" s="8"/>
     </row>
     <row r="115" ht="13.55" customHeight="1">
-      <c r="A115" t="s" s="5">
+      <c r="A115" t="s" s="6">
         <v>345</v>
       </c>
-      <c r="B115" s="7"/>
-      <c r="C115" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D115" s="6">
-        <v>570</v>
-      </c>
-      <c r="E115" t="s" s="5">
+      <c r="B115" s="8"/>
+      <c r="C115" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D115" s="7">
+        <v>570</v>
+      </c>
+      <c r="E115" t="s" s="6">
         <v>346</v>
       </c>
-      <c r="F115" t="b" s="6">
+      <c r="F115" t="b" s="7">
         <v>1</v>
       </c>
-      <c r="G115" s="6">
+      <c r="G115" s="7">
         <v>28.6326632621358</v>
       </c>
-      <c r="H115" s="6">
+      <c r="H115" s="7">
         <v>-105.974075888237</v>
       </c>
+      <c r="I115" s="8"/>
     </row>
     <row r="116" ht="13.55" customHeight="1">
-      <c r="A116" t="s" s="5">
+      <c r="A116" t="s" s="6">
         <v>347</v>
       </c>
-      <c r="B116" s="8">
+      <c r="B116" s="9">
         <v>41812</v>
       </c>
-      <c r="C116" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D116" s="6">
-        <v>570</v>
-      </c>
-      <c r="E116" t="s" s="5">
+      <c r="C116" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D116" s="7">
+        <v>570</v>
+      </c>
+      <c r="E116" t="s" s="6">
         <v>348</v>
       </c>
-      <c r="F116" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G116" s="6">
+      <c r="F116" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G116" s="7">
         <v>28.8643344388921</v>
       </c>
-      <c r="H116" s="6">
+      <c r="H116" s="7">
         <v>-106.225550619079</v>
       </c>
+      <c r="I116" s="8"/>
     </row>
     <row r="117" ht="13.55" customHeight="1">
-      <c r="A117" t="s" s="5">
+      <c r="A117" t="s" s="6">
         <v>349</v>
       </c>
-      <c r="B117" t="s" s="5">
+      <c r="B117" t="s" s="6">
         <v>350</v>
       </c>
-      <c r="C117" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D117" s="6">
-        <v>570</v>
-      </c>
-      <c r="E117" t="s" s="5">
+      <c r="C117" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D117" s="7">
+        <v>570</v>
+      </c>
+      <c r="E117" t="s" s="6">
         <v>351</v>
       </c>
-      <c r="F117" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G117" s="6">
+      <c r="F117" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G117" s="7">
         <v>28.6064627589729</v>
       </c>
-      <c r="H117" s="6">
+      <c r="H117" s="7">
         <v>-106.043151201727</v>
       </c>
+      <c r="I117" s="8"/>
     </row>
     <row r="118" ht="13.55" customHeight="1">
-      <c r="A118" t="s" s="5">
+      <c r="A118" t="s" s="6">
         <v>352</v>
       </c>
-      <c r="B118" t="s" s="5">
+      <c r="B118" t="s" s="6">
         <v>353</v>
       </c>
-      <c r="C118" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D118" s="6">
-        <v>570</v>
-      </c>
-      <c r="E118" t="s" s="5">
+      <c r="C118" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D118" s="7">
+        <v>570</v>
+      </c>
+      <c r="E118" t="s" s="6">
         <v>354</v>
       </c>
-      <c r="F118" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G118" s="6">
+      <c r="F118" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G118" s="7">
         <v>28.6235228194358</v>
       </c>
-      <c r="H118" s="6">
+      <c r="H118" s="7">
         <v>-106.029608508908</v>
       </c>
+      <c r="I118" s="8"/>
     </row>
     <row r="119" ht="13.55" customHeight="1">
-      <c r="A119" t="s" s="5">
+      <c r="A119" t="s" s="6">
         <v>355</v>
       </c>
-      <c r="B119" t="s" s="5">
+      <c r="B119" t="s" s="6">
         <v>356</v>
       </c>
-      <c r="C119" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D119" s="6">
-        <v>570</v>
-      </c>
-      <c r="E119" t="s" s="5">
+      <c r="C119" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D119" s="7">
+        <v>570</v>
+      </c>
+      <c r="E119" t="s" s="6">
         <v>357</v>
       </c>
-      <c r="F119" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G119" s="6">
+      <c r="F119" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G119" s="7">
         <v>28.657707043607</v>
       </c>
-      <c r="H119" s="6">
+      <c r="H119" s="7">
         <v>-106.093554225851</v>
       </c>
+      <c r="I119" s="8"/>
     </row>
     <row r="120" ht="13.55" customHeight="1">
-      <c r="A120" t="s" s="5">
+      <c r="A120" t="s" s="6">
         <v>358</v>
       </c>
-      <c r="B120" t="s" s="5">
+      <c r="B120" t="s" s="6">
         <v>359</v>
       </c>
-      <c r="C120" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D120" s="6">
-        <v>570</v>
-      </c>
-      <c r="E120" t="s" s="5">
+      <c r="C120" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D120" s="7">
+        <v>570</v>
+      </c>
+      <c r="E120" t="s" s="6">
         <v>360</v>
       </c>
-      <c r="F120" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G120" s="6">
+      <c r="F120" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G120" s="7">
         <v>28.618314783130</v>
       </c>
-      <c r="H120" s="6">
+      <c r="H120" s="7">
         <v>-106.058368661148</v>
       </c>
+      <c r="I120" s="8"/>
     </row>
     <row r="121" ht="13.55" customHeight="1">
-      <c r="A121" t="s" s="5">
+      <c r="A121" t="s" s="6">
         <v>361</v>
       </c>
-      <c r="B121" t="s" s="5">
+      <c r="B121" t="s" s="6">
         <v>362</v>
       </c>
-      <c r="C121" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D121" s="6">
-        <v>570</v>
-      </c>
-      <c r="E121" t="s" s="5">
+      <c r="C121" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D121" s="7">
+        <v>570</v>
+      </c>
+      <c r="E121" t="s" s="6">
         <v>363</v>
       </c>
-      <c r="F121" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G121" s="6">
+      <c r="F121" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G121" s="7">
         <v>28.6130045349287</v>
       </c>
-      <c r="H121" s="6">
+      <c r="H121" s="7">
         <v>-106.107250310755</v>
       </c>
+      <c r="I121" s="8"/>
     </row>
     <row r="122" ht="13.55" customHeight="1">
-      <c r="A122" t="s" s="5">
+      <c r="A122" t="s" s="6">
         <v>364</v>
       </c>
-      <c r="B122" t="s" s="5">
+      <c r="B122" t="s" s="6">
         <v>365</v>
       </c>
-      <c r="C122" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D122" s="6">
-        <v>570</v>
-      </c>
-      <c r="E122" t="s" s="5">
+      <c r="C122" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D122" s="7">
+        <v>570</v>
+      </c>
+      <c r="E122" t="s" s="6">
         <v>366</v>
       </c>
-      <c r="F122" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G122" s="6">
+      <c r="F122" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G122" s="7">
         <v>28.5974454382962</v>
       </c>
-      <c r="H122" s="6">
+      <c r="H122" s="7">
         <v>-106.032021464006</v>
       </c>
+      <c r="I122" s="8"/>
     </row>
     <row r="123" ht="13.55" customHeight="1">
-      <c r="A123" t="s" s="5">
+      <c r="A123" t="s" s="6">
         <v>367</v>
       </c>
-      <c r="B123" t="s" s="5">
+      <c r="B123" t="s" s="6">
         <v>368</v>
       </c>
-      <c r="C123" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D123" s="6">
-        <v>570</v>
-      </c>
-      <c r="E123" t="s" s="5">
+      <c r="C123" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D123" s="7">
+        <v>570</v>
+      </c>
+      <c r="E123" t="s" s="6">
         <v>369</v>
       </c>
-      <c r="F123" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G123" s="6">
+      <c r="F123" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G123" s="7">
         <v>28.6689567758541</v>
       </c>
-      <c r="H123" s="6">
+      <c r="H123" s="7">
         <v>-106.084470712959</v>
       </c>
+      <c r="I123" s="8"/>
     </row>
     <row r="124" ht="13.55" customHeight="1">
-      <c r="A124" t="s" s="5">
+      <c r="A124" t="s" s="6">
         <v>370</v>
       </c>
-      <c r="B124" t="s" s="5">
+      <c r="B124" t="s" s="6">
         <v>371</v>
       </c>
-      <c r="C124" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D124" s="6">
-        <v>570</v>
-      </c>
-      <c r="E124" t="s" s="5">
+      <c r="C124" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D124" s="7">
+        <v>570</v>
+      </c>
+      <c r="E124" t="s" s="6">
         <v>372</v>
       </c>
-      <c r="F124" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G124" s="6">
+      <c r="F124" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G124" s="7">
         <v>28.6358711543785</v>
       </c>
-      <c r="H124" s="6">
+      <c r="H124" s="7">
         <v>-106.068089340253</v>
       </c>
+      <c r="I124" s="8"/>
     </row>
     <row r="125" ht="13.55" customHeight="1">
-      <c r="A125" t="s" s="5">
+      <c r="A125" t="s" s="6">
         <v>373</v>
       </c>
-      <c r="B125" t="s" s="5">
+      <c r="B125" t="s" s="6">
         <v>374</v>
       </c>
-      <c r="C125" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D125" s="6">
-        <v>570</v>
-      </c>
-      <c r="E125" t="s" s="5">
+      <c r="C125" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D125" s="7">
+        <v>570</v>
+      </c>
+      <c r="E125" t="s" s="6">
         <v>375</v>
       </c>
-      <c r="F125" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G125" s="6">
+      <c r="F125" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G125" s="7">
         <v>28.7365899065499</v>
       </c>
-      <c r="H125" s="6">
+      <c r="H125" s="7">
         <v>-106.097963621096</v>
       </c>
+      <c r="I125" s="8"/>
     </row>
     <row r="126" ht="13.55" customHeight="1">
-      <c r="A126" t="s" s="5">
+      <c r="A126" t="s" s="6">
         <v>376</v>
       </c>
-      <c r="B126" t="s" s="5">
+      <c r="B126" t="s" s="6">
         <v>377</v>
       </c>
-      <c r="C126" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D126" s="6">
-        <v>570</v>
-      </c>
-      <c r="E126" t="s" s="5">
+      <c r="C126" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D126" s="7">
+        <v>570</v>
+      </c>
+      <c r="E126" t="s" s="6">
         <v>378</v>
       </c>
-      <c r="F126" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G126" s="6">
+      <c r="F126" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G126" s="7">
         <v>28.634056226559</v>
       </c>
-      <c r="H126" s="6">
+      <c r="H126" s="7">
         <v>-106.087035628992</v>
       </c>
+      <c r="I126" s="8"/>
     </row>
     <row r="127" ht="13.55" customHeight="1">
-      <c r="A127" t="s" s="5">
+      <c r="A127" t="s" s="6">
         <v>379</v>
       </c>
-      <c r="B127" t="s" s="5">
+      <c r="B127" t="s" s="6">
         <v>380</v>
       </c>
-      <c r="C127" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D127" s="6">
-        <v>570</v>
-      </c>
-      <c r="E127" t="s" s="5">
+      <c r="C127" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D127" s="7">
+        <v>570</v>
+      </c>
+      <c r="E127" t="s" s="6">
         <v>381</v>
       </c>
-      <c r="F127" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G127" s="6">
+      <c r="F127" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G127" s="7">
         <v>28.6018543305406</v>
       </c>
-      <c r="H127" s="6">
+      <c r="H127" s="7">
         <v>-106.038572788348</v>
       </c>
+      <c r="I127" s="8"/>
     </row>
     <row r="128" ht="13.55" customHeight="1">
-      <c r="A128" t="s" s="5">
+      <c r="A128" t="s" s="6">
         <v>382</v>
       </c>
-      <c r="B128" t="s" s="5">
+      <c r="B128" t="s" s="6">
         <v>383</v>
       </c>
-      <c r="C128" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D128" s="6">
-        <v>570</v>
-      </c>
-      <c r="E128" t="s" s="5">
+      <c r="C128" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D128" s="7">
+        <v>570</v>
+      </c>
+      <c r="E128" t="s" s="6">
         <v>384</v>
       </c>
-      <c r="F128" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G128" s="6">
+      <c r="F128" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G128" s="7">
         <v>28.7402795016556</v>
       </c>
-      <c r="H128" s="6">
+      <c r="H128" s="7">
         <v>-106.124518577421</v>
       </c>
+      <c r="I128" s="8"/>
     </row>
     <row r="129" ht="13.55" customHeight="1">
-      <c r="A129" t="s" s="5">
+      <c r="A129" t="s" s="6">
         <v>385</v>
       </c>
-      <c r="B129" t="s" s="5">
+      <c r="B129" t="s" s="6">
         <v>386</v>
       </c>
-      <c r="C129" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D129" s="6">
-        <v>570</v>
-      </c>
-      <c r="E129" t="s" s="5">
+      <c r="C129" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D129" s="7">
+        <v>570</v>
+      </c>
+      <c r="E129" t="s" s="6">
         <v>387</v>
       </c>
-      <c r="F129" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G129" s="6">
+      <c r="F129" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G129" s="7">
         <v>28.7132290061443</v>
       </c>
-      <c r="H129" s="6">
+      <c r="H129" s="7">
         <v>-106.085506289029</v>
       </c>
+      <c r="I129" s="8"/>
     </row>
     <row r="130" ht="13.55" customHeight="1">
-      <c r="A130" t="s" s="5">
+      <c r="A130" t="s" s="6">
         <v>388</v>
       </c>
-      <c r="B130" t="s" s="5">
+      <c r="B130" t="s" s="6">
         <v>389</v>
       </c>
-      <c r="C130" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D130" s="6">
-        <v>570</v>
-      </c>
-      <c r="E130" t="s" s="5">
+      <c r="C130" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D130" s="7">
+        <v>570</v>
+      </c>
+      <c r="E130" t="s" s="6">
         <v>390</v>
       </c>
-      <c r="F130" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G130" s="6">
+      <c r="F130" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G130" s="7">
         <v>28.7487855953139</v>
       </c>
-      <c r="H130" s="6">
+      <c r="H130" s="7">
         <v>-106.150299118897</v>
       </c>
+      <c r="I130" s="8"/>
     </row>
     <row r="131" ht="13.55" customHeight="1">
-      <c r="A131" t="s" s="5">
+      <c r="A131" t="s" s="6">
         <v>391</v>
       </c>
-      <c r="B131" t="s" s="5">
+      <c r="B131" t="s" s="6">
         <v>392</v>
       </c>
-      <c r="C131" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D131" s="6">
-        <v>570</v>
-      </c>
-      <c r="E131" t="s" s="5">
+      <c r="C131" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D131" s="7">
+        <v>570</v>
+      </c>
+      <c r="E131" t="s" s="6">
         <v>393</v>
       </c>
-      <c r="F131" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G131" s="6">
+      <c r="F131" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G131" s="7">
         <v>28.6461621732274</v>
       </c>
-      <c r="H131" s="6">
+      <c r="H131" s="7">
         <v>-106.134245940245</v>
       </c>
+      <c r="I131" s="8"/>
     </row>
     <row r="132" ht="13.55" customHeight="1">
-      <c r="A132" t="s" s="5">
+      <c r="A132" t="s" s="6">
         <v>394</v>
       </c>
-      <c r="B132" t="s" s="5">
+      <c r="B132" t="s" s="6">
         <v>395</v>
       </c>
-      <c r="C132" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D132" s="6">
-        <v>570</v>
-      </c>
-      <c r="E132" t="s" s="5">
+      <c r="C132" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D132" s="7">
+        <v>570</v>
+      </c>
+      <c r="E132" t="s" s="6">
         <v>396</v>
       </c>
-      <c r="F132" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G132" s="6">
+      <c r="F132" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G132" s="7">
         <v>28.6742207200737</v>
       </c>
-      <c r="H132" s="6">
+      <c r="H132" s="7">
         <v>-106.103035703770</v>
       </c>
+      <c r="I132" s="8"/>
     </row>
     <row r="133" ht="13.55" customHeight="1">
-      <c r="A133" t="s" s="5">
+      <c r="A133" t="s" s="6">
         <v>397</v>
       </c>
-      <c r="B133" t="s" s="5">
+      <c r="B133" t="s" s="6">
         <v>398</v>
       </c>
-      <c r="C133" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D133" s="6">
-        <v>570</v>
-      </c>
-      <c r="E133" t="s" s="5">
+      <c r="C133" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D133" s="7">
+        <v>570</v>
+      </c>
+      <c r="E133" t="s" s="6">
         <v>399</v>
       </c>
-      <c r="F133" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G133" s="6">
+      <c r="F133" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G133" s="7">
         <v>28.6540440987993</v>
       </c>
-      <c r="H133" s="6">
+      <c r="H133" s="7">
         <v>-105.960536233602</v>
       </c>
+      <c r="I133" s="8"/>
     </row>
     <row r="134" ht="13.55" customHeight="1">
-      <c r="A134" t="s" s="5">
+      <c r="A134" t="s" s="6">
         <v>400</v>
       </c>
-      <c r="B134" t="s" s="5">
+      <c r="B134" t="s" s="6">
         <v>401</v>
       </c>
-      <c r="C134" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D134" s="6">
-        <v>570</v>
-      </c>
-      <c r="E134" t="s" s="5">
+      <c r="C134" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D134" s="7">
+        <v>570</v>
+      </c>
+      <c r="E134" t="s" s="6">
         <v>402</v>
       </c>
-      <c r="F134" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G134" s="6">
+      <c r="F134" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G134" s="7">
         <v>28.7332927521261</v>
       </c>
-      <c r="H134" s="6">
+      <c r="H134" s="7">
         <v>-106.114411310864</v>
       </c>
+      <c r="I134" s="8"/>
     </row>
     <row r="135" ht="13.55" customHeight="1">
-      <c r="A135" t="s" s="5">
+      <c r="A135" t="s" s="6">
         <v>403</v>
       </c>
-      <c r="B135" t="s" s="5">
+      <c r="B135" t="s" s="6">
         <v>404</v>
       </c>
-      <c r="C135" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D135" s="6">
-        <v>570</v>
-      </c>
-      <c r="E135" t="s" s="5">
+      <c r="C135" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D135" s="7">
+        <v>570</v>
+      </c>
+      <c r="E135" t="s" s="6">
         <v>405</v>
       </c>
-      <c r="F135" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G135" s="6">
+      <c r="F135" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G135" s="7">
         <v>28.6149837411526</v>
       </c>
-      <c r="H135" s="6">
+      <c r="H135" s="7">
         <v>-106.032424849515</v>
       </c>
+      <c r="I135" s="8"/>
     </row>
     <row r="136" ht="13.55" customHeight="1">
-      <c r="A136" t="s" s="5">
+      <c r="A136" t="s" s="6">
         <v>406</v>
       </c>
-      <c r="B136" t="s" s="5">
+      <c r="B136" t="s" s="6">
         <v>407</v>
       </c>
-      <c r="C136" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D136" s="6">
-        <v>570</v>
-      </c>
-      <c r="E136" t="s" s="5">
+      <c r="C136" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D136" s="7">
+        <v>570</v>
+      </c>
+      <c r="E136" t="s" s="6">
         <v>408</v>
       </c>
-      <c r="F136" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G136" s="6">
+      <c r="F136" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G136" s="7">
         <v>28.8549102255006</v>
       </c>
-      <c r="H136" s="6">
+      <c r="H136" s="7">
         <v>-106.204053725049</v>
       </c>
+      <c r="I136" s="8"/>
     </row>
     <row r="137" ht="13.55" customHeight="1">
-      <c r="A137" t="s" s="5">
+      <c r="A137" t="s" s="6">
         <v>409</v>
       </c>
-      <c r="B137" t="s" s="5">
+      <c r="B137" t="s" s="6">
         <v>410</v>
       </c>
-      <c r="C137" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D137" s="6">
-        <v>570</v>
-      </c>
-      <c r="E137" t="s" s="5">
+      <c r="C137" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D137" s="7">
+        <v>570</v>
+      </c>
+      <c r="E137" t="s" s="6">
         <v>411</v>
       </c>
-      <c r="F137" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G137" s="6">
+      <c r="F137" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G137" s="7">
         <v>28.621613081270</v>
       </c>
-      <c r="H137" s="6">
+      <c r="H137" s="7">
         <v>-106.063313902644</v>
       </c>
+      <c r="I137" s="8"/>
     </row>
     <row r="138" ht="13.55" customHeight="1">
-      <c r="A138" t="s" s="5">
+      <c r="A138" t="s" s="6">
         <v>412</v>
       </c>
-      <c r="B138" t="s" s="5">
+      <c r="B138" t="s" s="6">
         <v>413</v>
       </c>
-      <c r="C138" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D138" s="6">
-        <v>570</v>
-      </c>
-      <c r="E138" t="s" s="5">
+      <c r="C138" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D138" s="7">
+        <v>570</v>
+      </c>
+      <c r="E138" t="s" s="6">
         <v>414</v>
       </c>
-      <c r="F138" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G138" s="6">
+      <c r="F138" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G138" s="7">
         <v>28.6140555559297</v>
       </c>
-      <c r="H138" s="6">
+      <c r="H138" s="7">
         <v>-106.073414421623</v>
       </c>
+      <c r="I138" s="8"/>
     </row>
     <row r="139" ht="13.55" customHeight="1">
-      <c r="A139" t="s" s="5">
+      <c r="A139" t="s" s="6">
         <v>415</v>
       </c>
-      <c r="B139" t="s" s="5">
+      <c r="B139" t="s" s="6">
         <v>416</v>
       </c>
-      <c r="C139" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D139" s="6">
-        <v>570</v>
-      </c>
-      <c r="E139" t="s" s="5">
+      <c r="C139" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D139" s="7">
+        <v>570</v>
+      </c>
+      <c r="E139" t="s" s="6">
         <v>417</v>
       </c>
-      <c r="F139" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G139" s="6">
+      <c r="F139" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G139" s="7">
         <v>28.6317286915189</v>
       </c>
-      <c r="H139" s="6">
+      <c r="H139" s="7">
         <v>-106.079334069711</v>
       </c>
+      <c r="I139" s="8"/>
     </row>
     <row r="140" ht="13.55" customHeight="1">
-      <c r="A140" t="s" s="5">
+      <c r="A140" t="s" s="6">
         <v>418</v>
       </c>
-      <c r="B140" t="s" s="5">
+      <c r="B140" t="s" s="6">
         <v>419</v>
       </c>
-      <c r="C140" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D140" s="6">
-        <v>570</v>
-      </c>
-      <c r="E140" t="s" s="5">
+      <c r="C140" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D140" s="7">
+        <v>570</v>
+      </c>
+      <c r="E140" t="s" s="6">
         <v>420</v>
       </c>
-      <c r="F140" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G140" s="6">
+      <c r="F140" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G140" s="7">
         <v>28.7291234586072</v>
       </c>
-      <c r="H140" s="6">
+      <c r="H140" s="7">
         <v>-106.095132887926</v>
       </c>
+      <c r="I140" s="8"/>
     </row>
     <row r="141" ht="13.55" customHeight="1">
-      <c r="A141" t="s" s="5">
+      <c r="A141" t="s" s="6">
         <v>421</v>
       </c>
-      <c r="B141" t="s" s="5">
+      <c r="B141" t="s" s="6">
         <v>422</v>
       </c>
-      <c r="C141" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D141" s="6">
-        <v>570</v>
-      </c>
-      <c r="E141" t="s" s="5">
+      <c r="C141" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D141" s="7">
+        <v>570</v>
+      </c>
+      <c r="E141" t="s" s="6">
         <v>423</v>
       </c>
-      <c r="F141" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G141" s="6">
+      <c r="F141" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G141" s="7">
         <v>28.6428583691931</v>
       </c>
-      <c r="H141" s="6">
+      <c r="H141" s="7">
         <v>-106.079201156682</v>
       </c>
+      <c r="I141" s="8"/>
     </row>
     <row r="142" ht="13.55" customHeight="1">
-      <c r="A142" t="s" s="5">
+      <c r="A142" t="s" s="6">
         <v>424</v>
       </c>
-      <c r="B142" t="s" s="5">
+      <c r="B142" t="s" s="6">
         <v>425</v>
       </c>
-      <c r="C142" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D142" s="6">
-        <v>570</v>
-      </c>
-      <c r="E142" t="s" s="5">
+      <c r="C142" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D142" s="7">
+        <v>570</v>
+      </c>
+      <c r="E142" t="s" s="6">
         <v>426</v>
       </c>
-      <c r="F142" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G142" s="6">
+      <c r="F142" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G142" s="7">
         <v>28.6535446426295</v>
       </c>
-      <c r="H142" s="6">
+      <c r="H142" s="7">
         <v>-106.099064562160</v>
       </c>
+      <c r="I142" s="8"/>
     </row>
     <row r="143" ht="13.55" customHeight="1">
-      <c r="A143" t="s" s="5">
+      <c r="A143" t="s" s="6">
         <v>427</v>
       </c>
-      <c r="B143" t="s" s="5">
+      <c r="B143" t="s" s="6">
         <v>428</v>
       </c>
-      <c r="C143" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D143" s="6">
-        <v>570</v>
-      </c>
-      <c r="E143" t="s" s="5">
+      <c r="C143" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D143" s="7">
+        <v>570</v>
+      </c>
+      <c r="E143" t="s" s="6">
         <v>429</v>
       </c>
-      <c r="F143" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G143" s="6">
+      <c r="F143" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G143" s="7">
         <v>28.6832100600955</v>
       </c>
-      <c r="H143" s="6">
+      <c r="H143" s="7">
         <v>-106.136428032442</v>
       </c>
+      <c r="I143" s="8"/>
     </row>
     <row r="144" ht="13.55" customHeight="1">
-      <c r="A144" t="s" s="5">
+      <c r="A144" t="s" s="6">
         <v>430</v>
       </c>
-      <c r="B144" t="s" s="5">
+      <c r="B144" t="s" s="6">
         <v>431</v>
       </c>
-      <c r="C144" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D144" s="6">
-        <v>570</v>
-      </c>
-      <c r="E144" t="s" s="5">
+      <c r="C144" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D144" s="7">
+        <v>570</v>
+      </c>
+      <c r="E144" t="s" s="6">
         <v>432</v>
       </c>
-      <c r="F144" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G144" s="6">
+      <c r="F144" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G144" s="7">
         <v>28.6826304798279</v>
       </c>
-      <c r="H144" s="6">
+      <c r="H144" s="7">
         <v>-106.109922593061</v>
       </c>
+      <c r="I144" s="8"/>
     </row>
     <row r="145" ht="13.55" customHeight="1">
-      <c r="A145" t="s" s="5">
+      <c r="A145" t="s" s="6">
         <v>433</v>
       </c>
-      <c r="B145" t="s" s="5">
+      <c r="B145" t="s" s="6">
         <v>434</v>
       </c>
-      <c r="C145" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D145" s="6">
-        <v>570</v>
-      </c>
-      <c r="E145" t="s" s="5">
+      <c r="C145" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D145" s="7">
+        <v>570</v>
+      </c>
+      <c r="E145" t="s" s="6">
         <v>435</v>
       </c>
-      <c r="F145" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G145" s="6">
+      <c r="F145" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G145" s="7">
         <v>28.6471533731568</v>
       </c>
-      <c r="H145" s="6">
+      <c r="H145" s="7">
         <v>-106.063838521748</v>
       </c>
+      <c r="I145" s="8"/>
     </row>
     <row r="146" ht="13.55" customHeight="1">
-      <c r="A146" t="s" s="5">
+      <c r="A146" t="s" s="6">
         <v>436</v>
       </c>
-      <c r="B146" t="s" s="5">
+      <c r="B146" t="s" s="6">
         <v>437</v>
       </c>
-      <c r="C146" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D146" s="6">
-        <v>570</v>
-      </c>
-      <c r="E146" t="s" s="5">
+      <c r="C146" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D146" s="7">
+        <v>570</v>
+      </c>
+      <c r="E146" t="s" s="6">
         <v>438</v>
       </c>
-      <c r="F146" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G146" s="6">
+      <c r="F146" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G146" s="7">
         <v>28.6345616596389</v>
       </c>
-      <c r="H146" s="6">
+      <c r="H146" s="7">
         <v>-106.097459265066</v>
       </c>
+      <c r="I146" s="8"/>
     </row>
     <row r="147" ht="13.55" customHeight="1">
-      <c r="A147" t="s" s="5">
+      <c r="A147" t="s" s="6">
         <v>439</v>
       </c>
-      <c r="B147" t="s" s="5">
+      <c r="B147" t="s" s="6">
         <v>440</v>
       </c>
-      <c r="C147" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D147" s="6">
-        <v>570</v>
-      </c>
-      <c r="E147" t="s" s="5">
+      <c r="C147" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D147" s="7">
+        <v>570</v>
+      </c>
+      <c r="E147" t="s" s="6">
         <v>441</v>
       </c>
-      <c r="F147" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G147" s="6">
+      <c r="F147" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G147" s="7">
         <v>28.6502737856342</v>
       </c>
-      <c r="H147" s="6">
+      <c r="H147" s="7">
         <v>-106.107896127106</v>
       </c>
+      <c r="I147" s="8"/>
     </row>
     <row r="148" ht="13.55" customHeight="1">
-      <c r="A148" t="s" s="5">
+      <c r="A148" t="s" s="6">
         <v>442</v>
       </c>
-      <c r="B148" t="s" s="5">
+      <c r="B148" t="s" s="6">
         <v>443</v>
       </c>
-      <c r="C148" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D148" s="6">
-        <v>570</v>
-      </c>
-      <c r="E148" t="s" s="5">
+      <c r="C148" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D148" s="7">
+        <v>570</v>
+      </c>
+      <c r="E148" t="s" s="6">
         <v>444</v>
       </c>
-      <c r="F148" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G148" s="6">
+      <c r="F148" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G148" s="7">
         <v>28.668744402597</v>
       </c>
-      <c r="H148" s="6">
+      <c r="H148" s="7">
         <v>-106.112260819973</v>
       </c>
+      <c r="I148" s="8"/>
     </row>
     <row r="149" ht="13.55" customHeight="1">
-      <c r="A149" t="s" s="5">
+      <c r="A149" t="s" s="6">
         <v>445</v>
       </c>
-      <c r="B149" t="s" s="5">
+      <c r="B149" t="s" s="6">
         <v>446</v>
       </c>
-      <c r="C149" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D149" s="6">
-        <v>570</v>
-      </c>
-      <c r="E149" t="s" s="5">
+      <c r="C149" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D149" s="7">
+        <v>570</v>
+      </c>
+      <c r="E149" t="s" s="6">
         <v>447</v>
       </c>
-      <c r="F149" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G149" s="6">
+      <c r="F149" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G149" s="7">
         <v>28.6699109683943</v>
       </c>
-      <c r="H149" s="6">
+      <c r="H149" s="7">
         <v>-105.978958913796</v>
       </c>
+      <c r="I149" s="8"/>
     </row>
     <row r="150" ht="13.55" customHeight="1">
-      <c r="A150" t="s" s="5">
+      <c r="A150" t="s" s="6">
         <v>448</v>
       </c>
-      <c r="B150" t="s" s="5">
+      <c r="B150" t="s" s="6">
         <v>449</v>
       </c>
-      <c r="C150" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D150" s="6">
-        <v>570</v>
-      </c>
-      <c r="E150" t="s" s="5">
+      <c r="C150" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D150" s="7">
+        <v>570</v>
+      </c>
+      <c r="E150" t="s" s="6">
         <v>450</v>
       </c>
-      <c r="F150" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G150" s="6">
+      <c r="F150" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G150" s="7">
         <v>28.6988980874263</v>
       </c>
-      <c r="H150" s="6">
+      <c r="H150" s="7">
         <v>-106.113957779526</v>
       </c>
+      <c r="I150" s="8"/>
     </row>
     <row r="151" ht="13.55" customHeight="1">
-      <c r="A151" t="s" s="5">
+      <c r="A151" t="s" s="6">
         <v>451</v>
       </c>
-      <c r="B151" t="s" s="5">
+      <c r="B151" t="s" s="6">
         <v>452</v>
       </c>
-      <c r="C151" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D151" s="6">
-        <v>570</v>
-      </c>
-      <c r="E151" t="s" s="5">
+      <c r="C151" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D151" s="7">
+        <v>570</v>
+      </c>
+      <c r="E151" t="s" s="6">
         <v>453</v>
       </c>
-      <c r="F151" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G151" s="6">
+      <c r="F151" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G151" s="7">
         <v>28.6556131935159</v>
       </c>
-      <c r="H151" s="6">
+      <c r="H151" s="7">
         <v>-106.091469757365</v>
       </c>
+      <c r="I151" s="8"/>
     </row>
     <row r="152" ht="13.55" customHeight="1">
-      <c r="A152" t="s" s="5">
+      <c r="A152" t="s" s="6">
         <v>454</v>
       </c>
-      <c r="B152" t="s" s="5">
+      <c r="B152" t="s" s="6">
         <v>455</v>
       </c>
-      <c r="C152" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D152" s="6">
-        <v>570</v>
-      </c>
-      <c r="E152" t="s" s="5">
+      <c r="C152" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D152" s="7">
+        <v>570</v>
+      </c>
+      <c r="E152" t="s" s="6">
         <v>456</v>
       </c>
-      <c r="F152" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G152" s="6">
+      <c r="F152" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G152" s="7">
         <v>28.7437489853496</v>
       </c>
-      <c r="H152" s="6">
+      <c r="H152" s="7">
         <v>-106.126237492114</v>
       </c>
+      <c r="I152" s="8"/>
     </row>
     <row r="153" ht="13.55" customHeight="1">
-      <c r="A153" t="s" s="5">
+      <c r="A153" t="s" s="6">
         <v>457</v>
       </c>
-      <c r="B153" t="s" s="5">
+      <c r="B153" t="s" s="6">
         <v>458</v>
       </c>
-      <c r="C153" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D153" s="6">
-        <v>570</v>
-      </c>
-      <c r="E153" t="s" s="5">
+      <c r="C153" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D153" s="7">
+        <v>570</v>
+      </c>
+      <c r="E153" t="s" s="6">
         <v>459</v>
       </c>
-      <c r="F153" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G153" s="6">
+      <c r="F153" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G153" s="7">
         <v>28.7122851833271</v>
       </c>
-      <c r="H153" s="6">
+      <c r="H153" s="7">
         <v>-106.134272031822</v>
       </c>
+      <c r="I153" s="8"/>
     </row>
     <row r="154" ht="13.55" customHeight="1">
-      <c r="A154" t="s" s="5">
+      <c r="A154" t="s" s="6">
         <v>460</v>
       </c>
-      <c r="B154" t="s" s="5">
+      <c r="B154" t="s" s="6">
         <v>461</v>
       </c>
-      <c r="C154" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D154" s="6">
-        <v>570</v>
-      </c>
-      <c r="E154" t="s" s="5">
+      <c r="C154" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D154" s="7">
+        <v>570</v>
+      </c>
+      <c r="E154" t="s" s="6">
         <v>462</v>
       </c>
-      <c r="F154" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G154" s="6">
+      <c r="F154" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G154" s="7">
         <v>28.6677458767455</v>
       </c>
-      <c r="H154" s="6">
+      <c r="H154" s="7">
         <v>-106.077804122049</v>
       </c>
+      <c r="I154" s="8"/>
     </row>
     <row r="155" ht="13.55" customHeight="1">
-      <c r="A155" t="s" s="5">
+      <c r="A155" t="s" s="6">
         <v>463</v>
       </c>
-      <c r="B155" t="s" s="5">
+      <c r="B155" t="s" s="6">
         <v>464</v>
       </c>
-      <c r="C155" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D155" s="6">
-        <v>570</v>
-      </c>
-      <c r="E155" t="s" s="5">
+      <c r="C155" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D155" s="7">
+        <v>570</v>
+      </c>
+      <c r="E155" t="s" s="6">
         <v>465</v>
       </c>
-      <c r="F155" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G155" s="6">
+      <c r="F155" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G155" s="7">
         <v>28.6697826858853</v>
       </c>
-      <c r="H155" s="6">
+      <c r="H155" s="7">
         <v>-106.102318325292</v>
       </c>
+      <c r="I155" s="8"/>
     </row>
     <row r="156" ht="13.55" customHeight="1">
-      <c r="A156" t="s" s="5">
+      <c r="A156" t="s" s="6">
         <v>466</v>
       </c>
-      <c r="B156" t="s" s="5">
+      <c r="B156" t="s" s="6">
         <v>467</v>
       </c>
-      <c r="C156" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D156" s="6">
-        <v>570</v>
-      </c>
-      <c r="E156" t="s" s="5">
+      <c r="C156" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D156" s="7">
+        <v>570</v>
+      </c>
+      <c r="E156" t="s" s="6">
         <v>468</v>
       </c>
-      <c r="F156" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G156" s="6">
+      <c r="F156" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G156" s="7">
         <v>28.6769080116526</v>
       </c>
-      <c r="H156" s="6">
+      <c r="H156" s="7">
         <v>-106.102054852203</v>
       </c>
+      <c r="I156" s="8"/>
     </row>
     <row r="157" ht="13.55" customHeight="1">
-      <c r="A157" t="s" s="5">
+      <c r="A157" t="s" s="6">
         <v>469</v>
       </c>
-      <c r="B157" t="s" s="5">
+      <c r="B157" t="s" s="6">
         <v>470</v>
       </c>
-      <c r="C157" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D157" s="6">
-        <v>570</v>
-      </c>
-      <c r="E157" t="s" s="5">
+      <c r="C157" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D157" s="7">
+        <v>570</v>
+      </c>
+      <c r="E157" t="s" s="6">
         <v>471</v>
       </c>
-      <c r="F157" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G157" s="6">
+      <c r="F157" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G157" s="7">
         <v>28.5980452624129</v>
       </c>
-      <c r="H157" s="6">
+      <c r="H157" s="7">
         <v>-106.099874907164</v>
       </c>
+      <c r="I157" s="8"/>
     </row>
     <row r="158" ht="13.55" customHeight="1">
-      <c r="A158" t="s" s="5">
+      <c r="A158" t="s" s="6">
         <v>472</v>
       </c>
-      <c r="B158" t="s" s="5">
+      <c r="B158" t="s" s="6">
         <v>473</v>
       </c>
-      <c r="C158" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D158" s="6">
-        <v>570</v>
-      </c>
-      <c r="E158" t="s" s="5">
+      <c r="C158" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D158" s="7">
+        <v>570</v>
+      </c>
+      <c r="E158" t="s" s="6">
         <v>474</v>
       </c>
-      <c r="F158" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G158" s="6">
+      <c r="F158" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G158" s="7">
         <v>28.5958329354846</v>
       </c>
-      <c r="H158" s="6">
+      <c r="H158" s="7">
         <v>-105.998716098373</v>
       </c>
+      <c r="I158" s="8"/>
     </row>
     <row r="159" ht="13.55" customHeight="1">
-      <c r="A159" t="s" s="5">
+      <c r="A159" t="s" s="6">
         <v>475</v>
       </c>
-      <c r="B159" t="s" s="5">
+      <c r="B159" t="s" s="6">
         <v>476</v>
       </c>
-      <c r="C159" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D159" s="6">
-        <v>570</v>
-      </c>
-      <c r="E159" t="s" s="5">
+      <c r="C159" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D159" s="7">
+        <v>570</v>
+      </c>
+      <c r="E159" t="s" s="6">
         <v>477</v>
       </c>
-      <c r="F159" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G159" s="6">
+      <c r="F159" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G159" s="7">
         <v>28.7251486749058</v>
       </c>
-      <c r="H159" s="6">
+      <c r="H159" s="7">
         <v>-106.110858477031</v>
       </c>
+      <c r="I159" s="8"/>
     </row>
     <row r="160" ht="13.55" customHeight="1">
-      <c r="A160" t="s" s="5">
+      <c r="A160" t="s" s="6">
         <v>478</v>
       </c>
-      <c r="B160" s="7"/>
-      <c r="C160" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D160" s="6">
-        <v>570</v>
-      </c>
-      <c r="E160" t="s" s="5">
+      <c r="B160" s="8"/>
+      <c r="C160" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D160" s="7">
+        <v>570</v>
+      </c>
+      <c r="E160" t="s" s="6">
         <v>479</v>
       </c>
-      <c r="F160" t="b" s="6">
+      <c r="F160" t="b" s="7">
         <v>1</v>
       </c>
-      <c r="G160" s="6">
+      <c r="G160" s="7">
         <v>28.6020399039605</v>
       </c>
-      <c r="H160" s="6">
+      <c r="H160" s="7">
         <v>-105.933534379901</v>
       </c>
+      <c r="I160" s="8"/>
     </row>
     <row r="161" ht="13.55" customHeight="1">
-      <c r="A161" t="s" s="5">
+      <c r="A161" t="s" s="6">
         <v>480</v>
       </c>
-      <c r="B161" t="s" s="5">
+      <c r="B161" t="s" s="6">
         <v>481</v>
       </c>
-      <c r="C161" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D161" s="6">
-        <v>570</v>
-      </c>
-      <c r="E161" t="s" s="5">
+      <c r="C161" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D161" s="7">
+        <v>570</v>
+      </c>
+      <c r="E161" t="s" s="6">
         <v>482</v>
       </c>
-      <c r="F161" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G161" s="6">
+      <c r="F161" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G161" s="7">
         <v>28.6259564115668</v>
       </c>
-      <c r="H161" s="6">
+      <c r="H161" s="7">
         <v>-106.075807357799</v>
       </c>
+      <c r="I161" s="8"/>
     </row>
     <row r="162" ht="13.55" customHeight="1">
-      <c r="A162" t="s" s="5">
+      <c r="A162" t="s" s="6">
         <v>483</v>
       </c>
-      <c r="B162" s="7"/>
-      <c r="C162" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D162" s="6">
-        <v>570</v>
-      </c>
-      <c r="E162" t="s" s="5">
+      <c r="B162" s="8"/>
+      <c r="C162" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D162" s="7">
+        <v>570</v>
+      </c>
+      <c r="E162" t="s" s="6">
         <v>484</v>
       </c>
-      <c r="F162" t="b" s="6">
+      <c r="F162" t="b" s="7">
         <v>1</v>
       </c>
-      <c r="G162" s="6">
+      <c r="G162" s="7">
         <v>28.7414885909305</v>
       </c>
-      <c r="H162" s="6">
+      <c r="H162" s="7">
         <v>-106.139722865355</v>
       </c>
+      <c r="I162" s="8"/>
     </row>
     <row r="163" ht="13.55" customHeight="1">
-      <c r="A163" t="s" s="5">
+      <c r="A163" t="s" s="6">
         <v>485</v>
       </c>
-      <c r="B163" t="s" s="5">
+      <c r="B163" t="s" s="6">
         <v>486</v>
       </c>
-      <c r="C163" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D163" s="6">
-        <v>570</v>
-      </c>
-      <c r="E163" t="s" s="5">
+      <c r="C163" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D163" s="7">
+        <v>570</v>
+      </c>
+      <c r="E163" t="s" s="6">
         <v>487</v>
       </c>
-      <c r="F163" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G163" s="6">
+      <c r="F163" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G163" s="7">
         <v>28.6640785509668</v>
       </c>
-      <c r="H163" s="6">
+      <c r="H163" s="7">
         <v>-105.940414762387</v>
       </c>
+      <c r="I163" s="8"/>
     </row>
     <row r="164" ht="13.55" customHeight="1">
-      <c r="A164" t="s" s="5">
+      <c r="A164" t="s" s="6">
         <v>488</v>
       </c>
-      <c r="B164" s="7"/>
-      <c r="C164" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D164" s="6">
-        <v>570</v>
-      </c>
-      <c r="E164" t="s" s="5">
+      <c r="B164" s="8"/>
+      <c r="C164" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D164" s="7">
+        <v>570</v>
+      </c>
+      <c r="E164" t="s" s="6">
         <v>489</v>
       </c>
-      <c r="F164" t="b" s="6">
+      <c r="F164" t="b" s="7">
         <v>1</v>
       </c>
-      <c r="G164" s="6">
+      <c r="G164" s="7">
         <v>28.6621214016378</v>
       </c>
-      <c r="H164" s="6">
+      <c r="H164" s="7">
         <v>-105.944961818804</v>
       </c>
+      <c r="I164" s="8"/>
     </row>
     <row r="165" ht="13.55" customHeight="1">
-      <c r="A165" t="s" s="5">
+      <c r="A165" t="s" s="6">
         <v>490</v>
       </c>
-      <c r="B165" t="s" s="5">
+      <c r="B165" t="s" s="6">
         <v>491</v>
       </c>
-      <c r="C165" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D165" s="6">
-        <v>570</v>
-      </c>
-      <c r="E165" t="s" s="5">
+      <c r="C165" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D165" s="7">
+        <v>570</v>
+      </c>
+      <c r="E165" t="s" s="6">
         <v>492</v>
       </c>
-      <c r="F165" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G165" s="6">
+      <c r="F165" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G165" s="7">
         <v>28.6749023014306</v>
       </c>
-      <c r="H165" s="6">
+      <c r="H165" s="7">
         <v>-105.982207684186</v>
       </c>
+      <c r="I165" s="8"/>
     </row>
     <row r="166" ht="13.55" customHeight="1">
-      <c r="A166" t="s" s="5">
+      <c r="A166" t="s" s="6">
         <v>493</v>
       </c>
-      <c r="B166" t="s" s="5">
+      <c r="B166" t="s" s="6">
         <v>494</v>
       </c>
-      <c r="C166" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D166" s="6">
-        <v>570</v>
-      </c>
-      <c r="E166" t="s" s="5">
+      <c r="C166" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D166" s="7">
+        <v>570</v>
+      </c>
+      <c r="E166" t="s" s="6">
         <v>495</v>
       </c>
-      <c r="F166" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G166" s="6">
+      <c r="F166" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G166" s="7">
         <v>28.624833507458</v>
       </c>
-      <c r="H166" s="6">
+      <c r="H166" s="7">
         <v>-106.099363911221</v>
       </c>
+      <c r="I166" s="8"/>
     </row>
     <row r="167" ht="13.55" customHeight="1">
-      <c r="A167" t="s" s="5">
+      <c r="A167" t="s" s="6">
         <v>496</v>
       </c>
-      <c r="B167" t="s" s="5">
+      <c r="B167" t="s" s="6">
         <v>497</v>
       </c>
-      <c r="C167" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D167" s="6">
-        <v>570</v>
-      </c>
-      <c r="E167" t="s" s="5">
+      <c r="C167" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D167" s="7">
+        <v>570</v>
+      </c>
+      <c r="E167" t="s" s="6">
         <v>498</v>
       </c>
-      <c r="F167" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G167" s="6">
+      <c r="F167" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G167" s="7">
         <v>28.5942307454286</v>
       </c>
-      <c r="H167" s="6">
+      <c r="H167" s="7">
         <v>-106.067625836948</v>
       </c>
+      <c r="I167" s="8"/>
     </row>
     <row r="168" ht="13.55" customHeight="1">
-      <c r="A168" t="s" s="5">
+      <c r="A168" t="s" s="6">
         <v>499</v>
       </c>
-      <c r="B168" t="s" s="5">
+      <c r="B168" t="s" s="6">
         <v>500</v>
       </c>
-      <c r="C168" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D168" s="6">
-        <v>570</v>
-      </c>
-      <c r="E168" t="s" s="5">
+      <c r="C168" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D168" s="7">
+        <v>570</v>
+      </c>
+      <c r="E168" t="s" s="6">
         <v>501</v>
       </c>
-      <c r="F168" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G168" s="6">
+      <c r="F168" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G168" s="7">
         <v>28.6068714854678</v>
       </c>
-      <c r="H168" s="6">
+      <c r="H168" s="7">
         <v>-106.011185458706</v>
       </c>
+      <c r="I168" s="8"/>
     </row>
     <row r="169" ht="13.55" customHeight="1">
-      <c r="A169" t="s" s="5">
+      <c r="A169" t="s" s="6">
         <v>502</v>
       </c>
-      <c r="B169" t="s" s="5">
+      <c r="B169" t="s" s="6">
         <v>503</v>
       </c>
-      <c r="C169" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D169" s="6">
-        <v>570</v>
-      </c>
-      <c r="E169" t="s" s="5">
+      <c r="C169" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D169" s="7">
+        <v>570</v>
+      </c>
+      <c r="E169" t="s" s="6">
         <v>504</v>
       </c>
-      <c r="F169" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G169" s="6">
+      <c r="F169" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G169" s="7">
         <v>28.7431759876022</v>
       </c>
-      <c r="H169" s="6">
+      <c r="H169" s="7">
         <v>-106.137895128007</v>
       </c>
+      <c r="I169" s="8"/>
     </row>
     <row r="170" ht="13.55" customHeight="1">
-      <c r="A170" t="s" s="5">
+      <c r="A170" t="s" s="6">
         <v>505</v>
       </c>
-      <c r="B170" t="s" s="5">
+      <c r="B170" t="s" s="6">
         <v>506</v>
       </c>
-      <c r="C170" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D170" s="6">
-        <v>570</v>
-      </c>
-      <c r="E170" t="s" s="5">
+      <c r="C170" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D170" s="7">
+        <v>570</v>
+      </c>
+      <c r="E170" t="s" s="6">
         <v>507</v>
       </c>
-      <c r="F170" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G170" s="6">
+      <c r="F170" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G170" s="7">
         <v>28.7336155777103</v>
       </c>
-      <c r="H170" s="6">
+      <c r="H170" s="7">
         <v>-106.104389173141</v>
       </c>
+      <c r="I170" s="8"/>
     </row>
     <row r="171" ht="13.55" customHeight="1">
-      <c r="A171" t="s" s="5">
+      <c r="A171" t="s" s="6">
         <v>508</v>
       </c>
-      <c r="B171" t="s" s="5">
+      <c r="B171" t="s" s="6">
         <v>509</v>
       </c>
-      <c r="C171" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D171" s="6">
-        <v>570</v>
-      </c>
-      <c r="E171" t="s" s="5">
+      <c r="C171" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D171" s="7">
+        <v>570</v>
+      </c>
+      <c r="E171" t="s" s="6">
         <v>510</v>
       </c>
-      <c r="F171" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G171" s="6">
+      <c r="F171" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G171" s="7">
         <v>28.651448151479</v>
       </c>
-      <c r="H171" s="6">
+      <c r="H171" s="7">
         <v>-106.069257003606</v>
       </c>
+      <c r="I171" s="8"/>
     </row>
     <row r="172" ht="13.55" customHeight="1">
-      <c r="A172" t="s" s="5">
+      <c r="A172" t="s" s="6">
         <v>511</v>
       </c>
-      <c r="B172" t="s" s="5">
+      <c r="B172" t="s" s="6">
         <v>512</v>
       </c>
-      <c r="C172" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D172" s="6">
-        <v>570</v>
-      </c>
-      <c r="E172" t="s" s="5">
+      <c r="C172" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D172" s="7">
+        <v>570</v>
+      </c>
+      <c r="E172" t="s" s="6">
         <v>513</v>
       </c>
-      <c r="F172" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G172" s="6">
+      <c r="F172" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G172" s="7">
         <v>28.7018653143882</v>
       </c>
-      <c r="H172" s="6">
+      <c r="H172" s="7">
         <v>-106.099955639843</v>
       </c>
+      <c r="I172" s="8"/>
     </row>
     <row r="173" ht="13.55" customHeight="1">
-      <c r="A173" t="s" s="5">
+      <c r="A173" t="s" s="6">
         <v>514</v>
       </c>
-      <c r="B173" t="s" s="5">
+      <c r="B173" t="s" s="6">
         <v>515</v>
       </c>
-      <c r="C173" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D173" s="6">
-        <v>570</v>
-      </c>
-      <c r="E173" t="s" s="5">
+      <c r="C173" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D173" s="7">
+        <v>570</v>
+      </c>
+      <c r="E173" t="s" s="6">
         <v>516</v>
       </c>
-      <c r="F173" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G173" s="6">
+      <c r="F173" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G173" s="7">
         <v>28.699005402346</v>
       </c>
-      <c r="H173" s="6">
+      <c r="H173" s="7">
         <v>-106.107128645212</v>
       </c>
+      <c r="I173" s="8"/>
     </row>
     <row r="174" ht="13.55" customHeight="1">
-      <c r="A174" t="s" s="5">
+      <c r="A174" t="s" s="6">
         <v>517</v>
       </c>
-      <c r="B174" t="s" s="5">
+      <c r="B174" t="s" s="6">
         <v>518</v>
       </c>
-      <c r="C174" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D174" s="6">
-        <v>570</v>
-      </c>
-      <c r="E174" t="s" s="5">
+      <c r="C174" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D174" s="7">
+        <v>570</v>
+      </c>
+      <c r="E174" t="s" s="6">
         <v>519</v>
       </c>
-      <c r="F174" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G174" s="6">
+      <c r="F174" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G174" s="7">
         <v>28.6847161618935</v>
       </c>
-      <c r="H174" s="6">
+      <c r="H174" s="7">
         <v>-106.142135576849</v>
       </c>
+      <c r="I174" s="8"/>
     </row>
     <row r="175" ht="13.55" customHeight="1">
-      <c r="A175" t="s" s="5">
+      <c r="A175" t="s" s="6">
         <v>520</v>
       </c>
-      <c r="B175" t="s" s="5">
+      <c r="B175" t="s" s="6">
         <v>521</v>
       </c>
-      <c r="C175" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D175" s="6">
-        <v>570</v>
-      </c>
-      <c r="E175" t="s" s="5">
+      <c r="C175" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D175" s="7">
+        <v>570</v>
+      </c>
+      <c r="E175" t="s" s="6">
         <v>522</v>
       </c>
-      <c r="F175" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G175" s="6">
+      <c r="F175" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G175" s="7">
         <v>28.6312811987524</v>
       </c>
-      <c r="H175" s="6">
+      <c r="H175" s="7">
         <v>-106.128282625251</v>
       </c>
+      <c r="I175" s="8"/>
     </row>
     <row r="176" ht="13.55" customHeight="1">
-      <c r="A176" t="s" s="5">
+      <c r="A176" t="s" s="6">
         <v>523</v>
       </c>
-      <c r="B176" t="s" s="5">
+      <c r="B176" t="s" s="6">
         <v>524</v>
       </c>
-      <c r="C176" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D176" s="6">
-        <v>570</v>
-      </c>
-      <c r="E176" t="s" s="5">
+      <c r="C176" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D176" s="7">
+        <v>570</v>
+      </c>
+      <c r="E176" t="s" s="6">
         <v>525</v>
       </c>
-      <c r="F176" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G176" s="6">
+      <c r="F176" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G176" s="7">
         <v>28.6807430897974</v>
       </c>
-      <c r="H176" s="6">
+      <c r="H176" s="7">
         <v>-106.098811828817</v>
       </c>
+      <c r="I176" s="8"/>
     </row>
     <row r="177" ht="13.55" customHeight="1">
-      <c r="A177" t="s" s="5">
+      <c r="A177" t="s" s="6">
         <v>526</v>
       </c>
-      <c r="B177" t="s" s="5">
+      <c r="B177" t="s" s="6">
         <v>527</v>
       </c>
-      <c r="C177" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D177" s="6">
-        <v>570</v>
-      </c>
-      <c r="E177" t="s" s="5">
+      <c r="C177" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D177" s="7">
+        <v>570</v>
+      </c>
+      <c r="E177" t="s" s="6">
         <v>528</v>
       </c>
-      <c r="F177" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G177" s="6">
+      <c r="F177" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G177" s="7">
         <v>28.6550254537011</v>
       </c>
-      <c r="H177" s="6">
+      <c r="H177" s="7">
         <v>-106.051855295601</v>
       </c>
+      <c r="I177" s="8"/>
     </row>
     <row r="178" ht="13.55" customHeight="1">
-      <c r="A178" t="s" s="5">
+      <c r="A178" t="s" s="6">
         <v>529</v>
       </c>
-      <c r="B178" t="s" s="5">
+      <c r="B178" t="s" s="6">
         <v>530</v>
       </c>
-      <c r="C178" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D178" s="6">
-        <v>570</v>
-      </c>
-      <c r="E178" t="s" s="5">
+      <c r="C178" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D178" s="7">
+        <v>570</v>
+      </c>
+      <c r="E178" t="s" s="6">
         <v>531</v>
       </c>
-      <c r="F178" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G178" s="6">
+      <c r="F178" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G178" s="7">
         <v>28.6736455976242</v>
       </c>
-      <c r="H178" s="6">
+      <c r="H178" s="7">
         <v>-106.109356819839</v>
       </c>
+      <c r="I178" s="8"/>
     </row>
     <row r="179" ht="13.55" customHeight="1">
-      <c r="A179" t="s" s="5">
+      <c r="A179" t="s" s="6">
         <v>532</v>
       </c>
-      <c r="B179" t="s" s="5">
+      <c r="B179" t="s" s="6">
         <v>533</v>
       </c>
-      <c r="C179" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D179" s="6">
-        <v>570</v>
-      </c>
-      <c r="E179" t="s" s="5">
+      <c r="C179" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D179" s="7">
+        <v>570</v>
+      </c>
+      <c r="E179" t="s" s="6">
         <v>534</v>
       </c>
-      <c r="F179" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G179" s="6">
+      <c r="F179" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G179" s="7">
         <v>28.6846807532722</v>
       </c>
-      <c r="H179" s="6">
+      <c r="H179" s="7">
         <v>-106.031289598801</v>
       </c>
+      <c r="I179" s="8"/>
     </row>
     <row r="180" ht="13.55" customHeight="1">
-      <c r="A180" t="s" s="5">
+      <c r="A180" t="s" s="6">
         <v>535</v>
       </c>
-      <c r="B180" t="s" s="5">
+      <c r="B180" t="s" s="6">
         <v>536</v>
       </c>
-      <c r="C180" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D180" s="6">
-        <v>570</v>
-      </c>
-      <c r="E180" t="s" s="5">
+      <c r="C180" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D180" s="7">
+        <v>570</v>
+      </c>
+      <c r="E180" t="s" s="6">
         <v>537</v>
       </c>
-      <c r="F180" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G180" s="6">
+      <c r="F180" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G180" s="7">
         <v>28.6467848976619</v>
       </c>
-      <c r="H180" s="6">
+      <c r="H180" s="7">
         <v>-106.062621333437</v>
       </c>
+      <c r="I180" s="8"/>
     </row>
     <row r="181" ht="13.55" customHeight="1">
-      <c r="A181" t="s" s="5">
+      <c r="A181" t="s" s="6">
         <v>538</v>
       </c>
-      <c r="B181" t="s" s="5">
+      <c r="B181" t="s" s="6">
         <v>539</v>
       </c>
-      <c r="C181" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D181" s="6">
-        <v>570</v>
-      </c>
-      <c r="E181" t="s" s="5">
+      <c r="C181" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D181" s="7">
+        <v>570</v>
+      </c>
+      <c r="E181" t="s" s="6">
         <v>540</v>
       </c>
-      <c r="F181" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G181" s="6">
+      <c r="F181" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G181" s="7">
         <v>28.6096574393917</v>
       </c>
-      <c r="H181" s="6">
+      <c r="H181" s="7">
         <v>-106.066078620535</v>
       </c>
+      <c r="I181" s="8"/>
     </row>
     <row r="182" ht="13.55" customHeight="1">
-      <c r="A182" t="s" s="5">
+      <c r="A182" t="s" s="6">
         <v>541</v>
       </c>
-      <c r="B182" t="s" s="5">
+      <c r="B182" t="s" s="6">
         <v>542</v>
       </c>
-      <c r="C182" s="7"/>
-      <c r="D182" s="6">
-        <v>570</v>
-      </c>
-      <c r="E182" t="s" s="5">
+      <c r="C182" s="8"/>
+      <c r="D182" s="7">
+        <v>570</v>
+      </c>
+      <c r="E182" t="s" s="6">
         <v>543</v>
       </c>
-      <c r="F182" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G182" s="6">
+      <c r="F182" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G182" s="7">
         <v>28.6652195651912</v>
       </c>
-      <c r="H182" s="6">
+      <c r="H182" s="7">
         <v>-106.091091851883</v>
       </c>
+      <c r="I182" s="8"/>
     </row>
     <row r="183" ht="13.55" customHeight="1">
-      <c r="A183" t="s" s="5">
+      <c r="A183" t="s" s="6">
         <v>544</v>
       </c>
-      <c r="B183" t="s" s="5">
+      <c r="B183" t="s" s="6">
         <v>545</v>
       </c>
-      <c r="C183" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D183" s="6">
-        <v>570</v>
-      </c>
-      <c r="E183" t="s" s="5">
+      <c r="C183" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D183" s="7">
+        <v>570</v>
+      </c>
+      <c r="E183" t="s" s="6">
         <v>546</v>
       </c>
-      <c r="F183" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G183" s="6">
+      <c r="F183" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G183" s="7">
         <v>28.6515166061123</v>
       </c>
-      <c r="H183" s="6">
+      <c r="H183" s="7">
         <v>-106.131339472123</v>
       </c>
+      <c r="I183" s="8"/>
     </row>
     <row r="184" ht="13.55" customHeight="1">
-      <c r="A184" t="s" s="5">
+      <c r="A184" t="s" s="6">
         <v>547</v>
       </c>
-      <c r="B184" t="s" s="5">
+      <c r="B184" t="s" s="6">
         <v>548</v>
       </c>
-      <c r="C184" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D184" s="6">
-        <v>570</v>
-      </c>
-      <c r="E184" t="s" s="5">
+      <c r="C184" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D184" s="7">
+        <v>570</v>
+      </c>
+      <c r="E184" t="s" s="6">
         <v>549</v>
       </c>
-      <c r="F184" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G184" s="6">
+      <c r="F184" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G184" s="7">
         <v>28.5602344831803</v>
       </c>
-      <c r="H184" s="6">
+      <c r="H184" s="7">
         <v>-105.9539851005</v>
       </c>
+      <c r="I184" s="8"/>
     </row>
     <row r="185" ht="13.55" customHeight="1">
-      <c r="A185" t="s" s="5">
+      <c r="A185" t="s" s="6">
         <v>550</v>
       </c>
-      <c r="B185" t="s" s="5">
+      <c r="B185" t="s" s="6">
         <v>551</v>
       </c>
-      <c r="C185" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D185" s="6">
-        <v>570</v>
-      </c>
-      <c r="E185" t="s" s="5">
+      <c r="C185" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D185" s="7">
+        <v>570</v>
+      </c>
+      <c r="E185" t="s" s="6">
         <v>552</v>
       </c>
-      <c r="F185" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G185" s="6">
+      <c r="F185" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G185" s="7">
         <v>28.7116281034817</v>
       </c>
-      <c r="H185" s="6">
+      <c r="H185" s="7">
         <v>-106.105648271902</v>
       </c>
+      <c r="I185" s="8"/>
     </row>
     <row r="186" ht="13.55" customHeight="1">
-      <c r="A186" t="s" s="5">
+      <c r="A186" t="s" s="6">
         <v>553</v>
       </c>
-      <c r="B186" t="s" s="5">
+      <c r="B186" t="s" s="6">
         <v>554</v>
       </c>
-      <c r="C186" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D186" s="6">
-        <v>570</v>
-      </c>
-      <c r="E186" t="s" s="5">
+      <c r="C186" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D186" s="7">
+        <v>570</v>
+      </c>
+      <c r="E186" t="s" s="6">
         <v>555</v>
       </c>
-      <c r="F186" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G186" s="6">
+      <c r="F186" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G186" s="7">
         <v>28.6278301052687</v>
       </c>
-      <c r="H186" s="6">
+      <c r="H186" s="7">
         <v>-106.054466953786</v>
       </c>
+      <c r="I186" s="8"/>
     </row>
     <row r="187" ht="13.55" customHeight="1">
-      <c r="A187" t="s" s="5">
+      <c r="A187" t="s" s="6">
         <v>556</v>
       </c>
-      <c r="B187" t="s" s="5">
+      <c r="B187" t="s" s="6">
         <v>557</v>
       </c>
-      <c r="C187" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D187" s="6">
-        <v>570</v>
-      </c>
-      <c r="E187" t="s" s="5">
+      <c r="C187" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D187" s="7">
+        <v>570</v>
+      </c>
+      <c r="E187" t="s" s="6">
         <v>558</v>
       </c>
-      <c r="F187" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G187" s="6">
+      <c r="F187" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G187" s="7">
         <v>28.7107663278357</v>
       </c>
-      <c r="H187" s="6">
+      <c r="H187" s="7">
         <v>-106.153226000281</v>
       </c>
+      <c r="I187" s="8"/>
     </row>
     <row r="188" ht="13.55" customHeight="1">
-      <c r="A188" t="s" s="5">
+      <c r="A188" t="s" s="6">
         <v>559</v>
       </c>
-      <c r="B188" t="s" s="5">
+      <c r="B188" t="s" s="6">
         <v>560</v>
       </c>
-      <c r="C188" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D188" s="6">
-        <v>570</v>
-      </c>
-      <c r="E188" t="s" s="5">
+      <c r="C188" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D188" s="7">
+        <v>570</v>
+      </c>
+      <c r="E188" t="s" s="6">
         <v>561</v>
       </c>
-      <c r="F188" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G188" s="6">
+      <c r="F188" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G188" s="7">
         <v>28.6730021348055</v>
       </c>
-      <c r="H188" s="6">
+      <c r="H188" s="7">
         <v>-106.026191807383</v>
       </c>
+      <c r="I188" s="8"/>
     </row>
     <row r="189" ht="13.55" customHeight="1">
-      <c r="A189" t="s" s="5">
+      <c r="A189" t="s" s="6">
         <v>562</v>
       </c>
-      <c r="B189" t="s" s="5">
+      <c r="B189" t="s" s="6">
         <v>563</v>
       </c>
-      <c r="C189" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D189" s="6">
-        <v>570</v>
-      </c>
-      <c r="E189" t="s" s="5">
+      <c r="C189" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D189" s="7">
+        <v>570</v>
+      </c>
+      <c r="E189" t="s" s="6">
         <v>564</v>
       </c>
-      <c r="F189" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G189" s="6">
+      <c r="F189" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G189" s="7">
         <v>28.6030729724175</v>
       </c>
-      <c r="H189" s="6">
+      <c r="H189" s="7">
         <v>-106.121023471924</v>
       </c>
+      <c r="I189" s="8"/>
     </row>
     <row r="190" ht="13.55" customHeight="1">
-      <c r="A190" t="s" s="5">
+      <c r="A190" t="s" s="6">
         <v>565</v>
       </c>
-      <c r="B190" s="7"/>
-      <c r="C190" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D190" s="6">
-        <v>570</v>
-      </c>
-      <c r="E190" t="s" s="5">
+      <c r="B190" s="8"/>
+      <c r="C190" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D190" s="7">
+        <v>570</v>
+      </c>
+      <c r="E190" t="s" s="6">
         <v>566</v>
       </c>
-      <c r="F190" t="b" s="6">
+      <c r="F190" t="b" s="7">
         <v>1</v>
       </c>
-      <c r="G190" s="6">
+      <c r="G190" s="7">
         <v>28.6251852773526</v>
       </c>
-      <c r="H190" s="6">
+      <c r="H190" s="7">
         <v>-106.083183864436</v>
       </c>
+      <c r="I190" s="8"/>
     </row>
     <row r="191" ht="13.55" customHeight="1">
-      <c r="A191" t="s" s="5">
+      <c r="A191" t="s" s="6">
         <v>567</v>
       </c>
-      <c r="B191" t="s" s="5">
+      <c r="B191" t="s" s="6">
         <v>568</v>
       </c>
-      <c r="C191" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D191" s="6">
-        <v>570</v>
-      </c>
-      <c r="E191" t="s" s="5">
+      <c r="C191" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D191" s="7">
+        <v>570</v>
+      </c>
+      <c r="E191" t="s" s="6">
         <v>569</v>
       </c>
-      <c r="F191" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G191" s="6">
+      <c r="F191" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G191" s="7">
         <v>28.6661894531743</v>
       </c>
-      <c r="H191" s="6">
+      <c r="H191" s="7">
         <v>-106.126819860173</v>
       </c>
+      <c r="I191" s="8"/>
     </row>
     <row r="192" ht="13.55" customHeight="1">
-      <c r="A192" t="s" s="5">
-        <v>570</v>
-      </c>
-      <c r="B192" t="s" s="5">
+      <c r="A192" t="s" s="6">
+        <v>570</v>
+      </c>
+      <c r="B192" t="s" s="6">
         <v>571</v>
       </c>
-      <c r="C192" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D192" s="6">
-        <v>570</v>
-      </c>
-      <c r="E192" t="s" s="5">
+      <c r="C192" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D192" s="7">
+        <v>570</v>
+      </c>
+      <c r="E192" t="s" s="6">
         <v>572</v>
       </c>
-      <c r="F192" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G192" s="6">
+      <c r="F192" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G192" s="7">
         <v>28.6464734409089</v>
       </c>
-      <c r="H192" s="6">
+      <c r="H192" s="7">
         <v>-106.125143013502</v>
       </c>
+      <c r="I192" s="8"/>
     </row>
     <row r="193" ht="13.55" customHeight="1">
-      <c r="A193" t="s" s="5">
+      <c r="A193" t="s" s="6">
         <v>573</v>
       </c>
-      <c r="B193" t="s" s="5">
+      <c r="B193" t="s" s="6">
         <v>574</v>
       </c>
-      <c r="C193" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D193" s="6">
-        <v>570</v>
-      </c>
-      <c r="E193" t="s" s="5">
+      <c r="C193" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D193" s="7">
+        <v>570</v>
+      </c>
+      <c r="E193" t="s" s="6">
         <v>575</v>
       </c>
-      <c r="F193" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G193" s="6">
+      <c r="F193" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G193" s="7">
         <v>28.6809018298403</v>
       </c>
-      <c r="H193" s="6">
+      <c r="H193" s="7">
         <v>-106.002408675189</v>
       </c>
+      <c r="I193" s="8"/>
     </row>
     <row r="194" ht="13.55" customHeight="1">
-      <c r="A194" t="s" s="5">
+      <c r="A194" t="s" s="6">
         <v>576</v>
       </c>
-      <c r="B194" t="s" s="5">
+      <c r="B194" t="s" s="6">
         <v>577</v>
       </c>
-      <c r="C194" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D194" s="6">
-        <v>570</v>
-      </c>
-      <c r="E194" t="s" s="5">
+      <c r="C194" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D194" s="7">
+        <v>570</v>
+      </c>
+      <c r="E194" t="s" s="6">
         <v>578</v>
       </c>
-      <c r="F194" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G194" s="6">
+      <c r="F194" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G194" s="7">
         <v>28.744002062396</v>
       </c>
-      <c r="H194" s="6">
+      <c r="H194" s="7">
         <v>-106.133549110884</v>
       </c>
+      <c r="I194" s="8"/>
     </row>
     <row r="195" ht="13.55" customHeight="1">
-      <c r="A195" t="s" s="5">
+      <c r="A195" t="s" s="6">
         <v>579</v>
       </c>
-      <c r="B195" t="s" s="5">
+      <c r="B195" t="s" s="6">
         <v>580</v>
       </c>
-      <c r="C195" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D195" s="6">
-        <v>570</v>
-      </c>
-      <c r="E195" t="s" s="5">
+      <c r="C195" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D195" s="7">
+        <v>570</v>
+      </c>
+      <c r="E195" t="s" s="6">
         <v>581</v>
       </c>
-      <c r="F195" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G195" s="6">
+      <c r="F195" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G195" s="7">
         <v>28.6032589563085</v>
       </c>
-      <c r="H195" s="6">
+      <c r="H195" s="7">
         <v>-106.101624444722</v>
       </c>
+      <c r="I195" s="8"/>
     </row>
     <row r="196" ht="13.55" customHeight="1">
-      <c r="A196" t="s" s="5">
+      <c r="A196" t="s" s="6">
         <v>582</v>
       </c>
-      <c r="B196" t="s" s="5">
+      <c r="B196" t="s" s="6">
         <v>583</v>
       </c>
-      <c r="C196" s="8">
+      <c r="C196" s="9">
         <v>41849</v>
       </c>
-      <c r="D196" s="7"/>
-      <c r="E196" t="s" s="5">
+      <c r="D196" s="8"/>
+      <c r="E196" t="s" s="6">
         <v>584</v>
       </c>
-      <c r="F196" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G196" s="6">
+      <c r="F196" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G196" s="7">
         <v>28.6274060961537</v>
       </c>
-      <c r="H196" s="6">
+      <c r="H196" s="7">
         <v>-105.951631019289</v>
       </c>
+      <c r="I196" s="8"/>
     </row>
     <row r="197" ht="13.55" customHeight="1">
-      <c r="A197" t="s" s="5">
+      <c r="A197" t="s" s="6">
         <v>585</v>
       </c>
-      <c r="B197" t="s" s="5">
+      <c r="B197" t="s" s="6">
         <v>586</v>
       </c>
-      <c r="C197" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D197" s="6">
-        <v>570</v>
-      </c>
-      <c r="E197" t="s" s="5">
+      <c r="C197" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D197" s="7">
+        <v>570</v>
+      </c>
+      <c r="E197" t="s" s="6">
         <v>587</v>
       </c>
-      <c r="F197" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G197" s="6">
+      <c r="F197" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G197" s="7">
         <v>28.7050752255224</v>
       </c>
-      <c r="H197" s="6">
+      <c r="H197" s="7">
         <v>-106.090180718637</v>
       </c>
+      <c r="I197" s="8"/>
     </row>
     <row r="198" ht="13.55" customHeight="1">
-      <c r="A198" t="s" s="5">
+      <c r="A198" t="s" s="6">
         <v>588</v>
       </c>
-      <c r="B198" t="s" s="5">
+      <c r="B198" t="s" s="6">
         <v>589</v>
       </c>
-      <c r="C198" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D198" s="6">
-        <v>570</v>
-      </c>
-      <c r="E198" t="s" s="5">
+      <c r="C198" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D198" s="7">
+        <v>570</v>
+      </c>
+      <c r="E198" t="s" s="6">
         <v>590</v>
       </c>
-      <c r="F198" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G198" s="6">
+      <c r="F198" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G198" s="7">
         <v>28.6196097153576</v>
       </c>
-      <c r="H198" s="6">
+      <c r="H198" s="7">
         <v>-106.108387633764</v>
       </c>
+      <c r="I198" s="8"/>
     </row>
     <row r="199" ht="13.55" customHeight="1">
-      <c r="A199" t="s" s="5">
+      <c r="A199" t="s" s="6">
         <v>591</v>
       </c>
-      <c r="B199" t="s" s="5">
+      <c r="B199" t="s" s="6">
         <v>592</v>
       </c>
-      <c r="C199" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D199" s="6">
-        <v>570</v>
-      </c>
-      <c r="E199" t="s" s="5">
+      <c r="C199" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D199" s="7">
+        <v>570</v>
+      </c>
+      <c r="E199" t="s" s="6">
         <v>593</v>
       </c>
-      <c r="F199" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G199" s="6">
+      <c r="F199" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G199" s="7">
         <v>28.6896920890227</v>
       </c>
-      <c r="H199" s="6">
+      <c r="H199" s="7">
         <v>-106.094238389167</v>
       </c>
+      <c r="I199" s="8"/>
     </row>
     <row r="200" ht="13.55" customHeight="1">
-      <c r="A200" t="s" s="5">
+      <c r="A200" t="s" s="6">
         <v>594</v>
       </c>
-      <c r="B200" t="s" s="5">
+      <c r="B200" t="s" s="6">
         <v>595</v>
       </c>
-      <c r="C200" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D200" s="6">
-        <v>570</v>
-      </c>
-      <c r="E200" t="s" s="5">
+      <c r="C200" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D200" s="7">
+        <v>570</v>
+      </c>
+      <c r="E200" t="s" s="6">
         <v>596</v>
       </c>
-      <c r="F200" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G200" s="6">
+      <c r="F200" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G200" s="7">
         <v>28.6447080500507</v>
       </c>
-      <c r="H200" s="6">
+      <c r="H200" s="7">
         <v>-106.078437166423</v>
       </c>
+      <c r="I200" s="8"/>
     </row>
     <row r="201" ht="13.55" customHeight="1">
-      <c r="A201" t="s" s="5">
+      <c r="A201" t="s" s="6">
         <v>597</v>
       </c>
-      <c r="B201" t="s" s="5">
+      <c r="B201" t="s" s="6">
         <v>598</v>
       </c>
-      <c r="C201" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D201" s="6">
-        <v>570</v>
-      </c>
-      <c r="E201" t="s" s="5">
+      <c r="C201" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D201" s="7">
+        <v>570</v>
+      </c>
+      <c r="E201" t="s" s="6">
         <v>599</v>
       </c>
-      <c r="F201" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G201" s="6">
+      <c r="F201" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G201" s="7">
         <v>28.767451848624</v>
       </c>
-      <c r="H201" s="6">
+      <c r="H201" s="7">
         <v>-106.169592086027</v>
       </c>
+      <c r="I201" s="8"/>
     </row>
     <row r="202" ht="13.55" customHeight="1">
-      <c r="A202" t="s" s="5">
+      <c r="A202" t="s" s="6">
         <v>600</v>
       </c>
-      <c r="B202" t="s" s="5">
+      <c r="B202" t="s" s="6">
         <v>601</v>
       </c>
-      <c r="C202" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D202" s="6">
-        <v>570</v>
-      </c>
-      <c r="E202" t="s" s="5">
+      <c r="C202" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D202" s="7">
+        <v>570</v>
+      </c>
+      <c r="E202" t="s" s="6">
         <v>602</v>
       </c>
-      <c r="F202" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G202" s="6">
+      <c r="F202" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G202" s="7">
         <v>28.6341779062661</v>
       </c>
-      <c r="H202" s="6">
+      <c r="H202" s="7">
         <v>-106.065627128143</v>
       </c>
+      <c r="I202" s="8"/>
     </row>
     <row r="203" ht="13.55" customHeight="1">
-      <c r="A203" t="s" s="5">
+      <c r="A203" t="s" s="6">
         <v>603</v>
       </c>
-      <c r="B203" t="s" s="5">
+      <c r="B203" t="s" s="6">
         <v>604</v>
       </c>
-      <c r="C203" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D203" s="6">
-        <v>570</v>
-      </c>
-      <c r="E203" t="s" s="5">
+      <c r="C203" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D203" s="7">
+        <v>570</v>
+      </c>
+      <c r="E203" t="s" s="6">
         <v>605</v>
       </c>
-      <c r="F203" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G203" s="6">
+      <c r="F203" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G203" s="7">
         <v>28.6663487420301</v>
       </c>
-      <c r="H203" s="6">
+      <c r="H203" s="7">
         <v>-106.098748782720</v>
       </c>
+      <c r="I203" s="8"/>
     </row>
     <row r="204" ht="13.55" customHeight="1">
-      <c r="A204" t="s" s="5">
+      <c r="A204" t="s" s="6">
         <v>606</v>
       </c>
-      <c r="B204" s="7"/>
-      <c r="C204" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D204" s="6">
-        <v>570</v>
-      </c>
-      <c r="E204" t="s" s="5">
+      <c r="B204" s="8"/>
+      <c r="C204" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D204" s="7">
+        <v>570</v>
+      </c>
+      <c r="E204" t="s" s="6">
         <v>607</v>
       </c>
-      <c r="F204" t="b" s="6">
+      <c r="F204" t="b" s="7">
         <v>1</v>
       </c>
-      <c r="G204" s="6">
+      <c r="G204" s="7">
         <v>28.6587661279892</v>
       </c>
-      <c r="H204" s="6">
+      <c r="H204" s="7">
         <v>-106.130472570266</v>
       </c>
+      <c r="I204" s="8"/>
     </row>
     <row r="205" ht="13.55" customHeight="1">
-      <c r="A205" t="s" s="5">
+      <c r="A205" t="s" s="6">
         <v>608</v>
       </c>
-      <c r="B205" s="8">
+      <c r="B205" s="9">
         <v>41811</v>
       </c>
-      <c r="C205" s="7"/>
-      <c r="D205" s="6">
-        <v>570</v>
-      </c>
-      <c r="E205" t="s" s="5">
+      <c r="C205" s="8"/>
+      <c r="D205" s="7">
+        <v>570</v>
+      </c>
+      <c r="E205" t="s" s="6">
         <v>609</v>
       </c>
-      <c r="F205" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G205" s="6">
+      <c r="F205" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G205" s="7">
         <v>28.6559397696576</v>
       </c>
-      <c r="H205" s="6">
+      <c r="H205" s="7">
         <v>-106.149336409497</v>
       </c>
+      <c r="I205" s="8"/>
     </row>
     <row r="206" ht="13.55" customHeight="1">
-      <c r="A206" t="s" s="5">
+      <c r="A206" t="s" s="6">
         <v>610</v>
       </c>
-      <c r="B206" t="s" s="5">
+      <c r="B206" t="s" s="6">
         <v>611</v>
       </c>
-      <c r="C206" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D206" s="6">
-        <v>570</v>
-      </c>
-      <c r="E206" t="s" s="5">
+      <c r="C206" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D206" s="7">
+        <v>570</v>
+      </c>
+      <c r="E206" t="s" s="6">
         <v>612</v>
       </c>
-      <c r="F206" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G206" s="6">
+      <c r="F206" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G206" s="7">
         <v>28.6360385151415</v>
       </c>
-      <c r="H206" s="6">
+      <c r="H206" s="7">
         <v>-106.089471503533</v>
       </c>
+      <c r="I206" s="8"/>
     </row>
     <row r="207" ht="13.55" customHeight="1">
-      <c r="A207" t="s" s="5">
+      <c r="A207" t="s" s="6">
         <v>613</v>
       </c>
-      <c r="B207" t="s" s="5">
+      <c r="B207" t="s" s="6">
         <v>614</v>
       </c>
-      <c r="C207" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D207" s="6">
-        <v>570</v>
-      </c>
-      <c r="E207" t="s" s="5">
+      <c r="C207" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D207" s="7">
+        <v>570</v>
+      </c>
+      <c r="E207" t="s" s="6">
         <v>615</v>
       </c>
-      <c r="F207" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G207" s="6">
+      <c r="F207" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G207" s="7">
         <v>28.6002998187639</v>
       </c>
-      <c r="H207" s="6">
+      <c r="H207" s="7">
         <v>-106.102373960859</v>
       </c>
+      <c r="I207" s="8"/>
     </row>
     <row r="208" ht="13.55" customHeight="1">
-      <c r="A208" t="s" s="5">
+      <c r="A208" t="s" s="6">
         <v>616</v>
       </c>
-      <c r="B208" t="s" s="5">
+      <c r="B208" t="s" s="6">
         <v>617</v>
       </c>
-      <c r="C208" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D208" s="6">
-        <v>570</v>
-      </c>
-      <c r="E208" t="s" s="5">
+      <c r="C208" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D208" s="7">
+        <v>570</v>
+      </c>
+      <c r="E208" t="s" s="6">
         <v>618</v>
       </c>
-      <c r="F208" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G208" s="6">
+      <c r="F208" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G208" s="7">
         <v>28.6469350232551</v>
       </c>
-      <c r="H208" s="6">
+      <c r="H208" s="7">
         <v>-106.069080953127</v>
       </c>
+      <c r="I208" s="8"/>
     </row>
     <row r="209" ht="13.55" customHeight="1">
-      <c r="A209" t="s" s="5">
+      <c r="A209" t="s" s="6">
         <v>619</v>
       </c>
-      <c r="B209" t="s" s="5">
+      <c r="B209" t="s" s="6">
         <v>620</v>
       </c>
-      <c r="C209" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D209" s="6">
-        <v>570</v>
-      </c>
-      <c r="E209" t="s" s="5">
+      <c r="C209" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D209" s="7">
+        <v>570</v>
+      </c>
+      <c r="E209" t="s" s="6">
         <v>621</v>
       </c>
-      <c r="F209" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G209" s="6">
+      <c r="F209" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G209" s="7">
         <v>28.6905464831132</v>
       </c>
-      <c r="H209" s="6">
+      <c r="H209" s="7">
         <v>-106.112475418059</v>
       </c>
+      <c r="I209" s="8"/>
     </row>
     <row r="210" ht="13.55" customHeight="1">
-      <c r="A210" t="s" s="5">
+      <c r="A210" t="s" s="6">
         <v>622</v>
       </c>
-      <c r="B210" t="s" s="5">
+      <c r="B210" t="s" s="6">
         <v>623</v>
       </c>
-      <c r="C210" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D210" s="6">
-        <v>570</v>
-      </c>
-      <c r="E210" t="s" s="5">
+      <c r="C210" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D210" s="7">
+        <v>570</v>
+      </c>
+      <c r="E210" t="s" s="6">
         <v>624</v>
       </c>
-      <c r="F210" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G210" s="6">
+      <c r="F210" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G210" s="7">
         <v>28.7490411316393</v>
       </c>
-      <c r="H210" s="6">
+      <c r="H210" s="7">
         <v>-106.128576637062</v>
       </c>
+      <c r="I210" s="8"/>
     </row>
     <row r="211" ht="13.55" customHeight="1">
-      <c r="A211" t="s" s="5">
+      <c r="A211" t="s" s="6">
         <v>625</v>
       </c>
-      <c r="B211" t="s" s="5">
+      <c r="B211" t="s" s="6">
         <v>626</v>
       </c>
-      <c r="C211" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D211" s="6">
-        <v>570</v>
-      </c>
-      <c r="E211" t="s" s="5">
+      <c r="C211" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D211" s="7">
+        <v>570</v>
+      </c>
+      <c r="E211" t="s" s="6">
         <v>627</v>
       </c>
-      <c r="F211" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G211" s="6">
+      <c r="F211" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G211" s="7">
         <v>28.6915888078454</v>
       </c>
-      <c r="H211" s="6">
+      <c r="H211" s="7">
         <v>-106.138209651951</v>
       </c>
+      <c r="I211" s="8"/>
     </row>
     <row r="212" ht="13.55" customHeight="1">
-      <c r="A212" t="s" s="5">
+      <c r="A212" t="s" s="6">
         <v>628</v>
       </c>
-      <c r="B212" t="s" s="5">
+      <c r="B212" t="s" s="6">
         <v>629</v>
       </c>
-      <c r="C212" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D212" s="6">
-        <v>570</v>
-      </c>
-      <c r="E212" t="s" s="5">
+      <c r="C212" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D212" s="7">
+        <v>570</v>
+      </c>
+      <c r="E212" t="s" s="6">
         <v>630</v>
       </c>
-      <c r="F212" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G212" s="6">
+      <c r="F212" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G212" s="7">
         <v>28.7366938580486</v>
       </c>
-      <c r="H212" s="6">
+      <c r="H212" s="7">
         <v>-106.122994395225</v>
       </c>
+      <c r="I212" s="8"/>
     </row>
     <row r="213" ht="13.55" customHeight="1">
-      <c r="A213" t="s" s="5">
+      <c r="A213" t="s" s="6">
         <v>631</v>
       </c>
-      <c r="B213" t="s" s="5">
+      <c r="B213" t="s" s="6">
         <v>632</v>
       </c>
-      <c r="C213" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D213" s="6">
-        <v>570</v>
-      </c>
-      <c r="E213" t="s" s="5">
+      <c r="C213" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D213" s="7">
+        <v>570</v>
+      </c>
+      <c r="E213" t="s" s="6">
         <v>633</v>
       </c>
-      <c r="F213" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G213" s="6">
+      <c r="F213" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G213" s="7">
         <v>28.6988229570778</v>
       </c>
-      <c r="H213" s="6">
+      <c r="H213" s="7">
         <v>-106.145334024850</v>
       </c>
+      <c r="I213" s="8"/>
     </row>
     <row r="214" ht="13.55" customHeight="1">
-      <c r="A214" t="s" s="5">
+      <c r="A214" t="s" s="6">
         <v>634</v>
       </c>
-      <c r="B214" t="s" s="5">
+      <c r="B214" t="s" s="6">
         <v>635</v>
       </c>
-      <c r="C214" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D214" s="6">
-        <v>570</v>
-      </c>
-      <c r="E214" t="s" s="5">
+      <c r="C214" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D214" s="7">
+        <v>570</v>
+      </c>
+      <c r="E214" t="s" s="6">
         <v>636</v>
       </c>
-      <c r="F214" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G214" s="6">
+      <c r="F214" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G214" s="7">
         <v>28.6297750213367</v>
       </c>
-      <c r="H214" s="6">
+      <c r="H214" s="7">
         <v>-105.956693294799</v>
       </c>
+      <c r="I214" s="8"/>
     </row>
     <row r="215" ht="13.55" customHeight="1">
-      <c r="A215" t="s" s="5">
+      <c r="A215" t="s" s="6">
         <v>637</v>
       </c>
-      <c r="B215" t="s" s="5">
+      <c r="B215" t="s" s="6">
         <v>638</v>
       </c>
-      <c r="C215" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D215" s="6">
-        <v>570</v>
-      </c>
-      <c r="E215" t="s" s="5">
+      <c r="C215" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D215" s="7">
+        <v>570</v>
+      </c>
+      <c r="E215" t="s" s="6">
         <v>639</v>
       </c>
-      <c r="F215" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G215" s="6">
+      <c r="F215" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G215" s="7">
         <v>28.7871518896538</v>
       </c>
-      <c r="H215" s="6">
+      <c r="H215" s="7">
         <v>-106.158120744468</v>
       </c>
+      <c r="I215" s="8"/>
     </row>
     <row r="216" ht="13.55" customHeight="1">
-      <c r="A216" t="s" s="5">
+      <c r="A216" t="s" s="6">
         <v>640</v>
       </c>
-      <c r="B216" t="s" s="5">
+      <c r="B216" t="s" s="6">
         <v>641</v>
       </c>
-      <c r="C216" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D216" s="6">
-        <v>570</v>
-      </c>
-      <c r="E216" t="s" s="5">
+      <c r="C216" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D216" s="7">
+        <v>570</v>
+      </c>
+      <c r="E216" t="s" s="6">
         <v>642</v>
       </c>
-      <c r="F216" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G216" s="6">
+      <c r="F216" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G216" s="7">
         <v>28.6275142932184</v>
       </c>
-      <c r="H216" s="6">
+      <c r="H216" s="7">
         <v>-106.118475101809</v>
       </c>
+      <c r="I216" s="8"/>
     </row>
     <row r="217" ht="13.55" customHeight="1">
-      <c r="A217" t="s" s="5">
+      <c r="A217" t="s" s="6">
         <v>643</v>
       </c>
-      <c r="B217" t="s" s="5">
+      <c r="B217" t="s" s="6">
         <v>644</v>
       </c>
-      <c r="C217" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D217" s="6">
-        <v>570</v>
-      </c>
-      <c r="E217" t="s" s="5">
+      <c r="C217" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D217" s="7">
+        <v>570</v>
+      </c>
+      <c r="E217" t="s" s="6">
         <v>645</v>
       </c>
-      <c r="F217" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G217" s="6">
+      <c r="F217" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G217" s="7">
         <v>28.6342928226382</v>
       </c>
-      <c r="H217" s="6">
+      <c r="H217" s="7">
         <v>-106.038969419174</v>
       </c>
+      <c r="I217" s="8"/>
     </row>
     <row r="218" ht="13.55" customHeight="1">
-      <c r="A218" t="s" s="5">
+      <c r="A218" t="s" s="6">
         <v>646</v>
       </c>
-      <c r="B218" t="s" s="5">
+      <c r="B218" t="s" s="6">
         <v>647</v>
       </c>
-      <c r="C218" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D218" s="6">
-        <v>570</v>
-      </c>
-      <c r="E218" t="s" s="5">
+      <c r="C218" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D218" s="7">
+        <v>570</v>
+      </c>
+      <c r="E218" t="s" s="6">
         <v>648</v>
       </c>
-      <c r="F218" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G218" s="6">
+      <c r="F218" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G218" s="7">
         <v>28.6724446270826</v>
       </c>
-      <c r="H218" s="6">
+      <c r="H218" s="7">
         <v>-106.106361183846</v>
       </c>
+      <c r="I218" s="8"/>
     </row>
     <row r="219" ht="13.55" customHeight="1">
-      <c r="A219" t="s" s="5">
+      <c r="A219" t="s" s="6">
         <v>649</v>
       </c>
-      <c r="B219" t="s" s="5">
+      <c r="B219" t="s" s="6">
         <v>650</v>
       </c>
-      <c r="C219" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D219" s="6">
-        <v>570</v>
-      </c>
-      <c r="E219" t="s" s="5">
+      <c r="C219" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D219" s="7">
+        <v>570</v>
+      </c>
+      <c r="E219" t="s" s="6">
         <v>651</v>
       </c>
-      <c r="F219" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G219" s="6">
+      <c r="F219" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G219" s="7">
         <v>28.6119996999256</v>
       </c>
-      <c r="H219" s="6">
+      <c r="H219" s="7">
         <v>-106.090406172807</v>
       </c>
+      <c r="I219" s="8"/>
     </row>
     <row r="220" ht="13.55" customHeight="1">
-      <c r="A220" t="s" s="5">
+      <c r="A220" t="s" s="6">
         <v>652</v>
       </c>
-      <c r="B220" t="s" s="5">
+      <c r="B220" t="s" s="6">
         <v>653</v>
       </c>
-      <c r="C220" t="s" s="5">
-        <v>10</v>
-      </c>
-      <c r="D220" s="6">
-        <v>570</v>
-      </c>
-      <c r="E220" t="s" s="5">
+      <c r="C220" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D220" s="7">
+        <v>570</v>
+      </c>
+      <c r="E220" t="s" s="6">
         <v>654</v>
       </c>
-      <c r="F220" t="b" s="6">
-        <v>0</v>
-      </c>
-      <c r="G220" s="6">
+      <c r="F220" t="b" s="7">
+        <v>0</v>
+      </c>
+      <c r="G220" s="7">
         <v>28.5843496169644</v>
       </c>
-      <c r="H220" s="6">
+      <c r="H220" s="7">
         <v>-106.102135908174</v>
       </c>
+      <c r="I220" s="8"/>
     </row>
     <row r="221" ht="13.55" customHeight="1">
-      <c r="A221" s="5"/>
-      <c r="B221" s="7"/>
-      <c r="C221" s="5"/>
-      <c r="D221" s="7"/>
-      <c r="E221" s="5"/>
-      <c r="F221" s="7"/>
-      <c r="G221" s="7"/>
-      <c r="H221" s="7"/>
+      <c r="A221" t="s" s="6">
+        <v>655</v>
+      </c>
+      <c r="B221" s="8"/>
+      <c r="C221" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D221" s="8"/>
+      <c r="E221" s="6"/>
+      <c r="F221" s="8"/>
+      <c r="G221" s="7">
+        <v>28.6997798670172</v>
+      </c>
+      <c r="H221" s="7">
+        <v>-106.033040971681</v>
+      </c>
+      <c r="I221" s="8"/>
     </row>
     <row r="222" ht="13.55" customHeight="1">
-      <c r="A222" s="5"/>
-      <c r="B222" s="7"/>
-      <c r="C222" s="5"/>
-      <c r="D222" s="7"/>
-      <c r="E222" s="5"/>
-      <c r="F222" s="7"/>
-      <c r="G222" s="7"/>
-      <c r="H222" s="7"/>
+      <c r="A222" t="s" s="6">
+        <v>656</v>
+      </c>
+      <c r="B222" s="8"/>
+      <c r="C222" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D222" s="8"/>
+      <c r="E222" s="6"/>
+      <c r="F222" s="8"/>
+      <c r="G222" s="7">
+        <v>28.692237803752</v>
+      </c>
+      <c r="H222" s="7">
+        <v>-106.121332162343</v>
+      </c>
+      <c r="I222" s="8"/>
     </row>
     <row r="223" ht="13.55" customHeight="1">
-      <c r="A223" s="5"/>
-      <c r="B223" s="7"/>
-      <c r="C223" s="5"/>
-      <c r="D223" s="7"/>
-      <c r="E223" s="5"/>
-      <c r="F223" s="7"/>
-      <c r="G223" s="7"/>
-      <c r="H223" s="7"/>
+      <c r="A223" s="6"/>
+      <c r="B223" s="8"/>
+      <c r="C223" s="6"/>
+      <c r="D223" s="8"/>
+      <c r="E223" s="6"/>
+      <c r="F223" s="8"/>
+      <c r="G223" s="8"/>
+      <c r="H223" s="8"/>
+      <c r="I223" s="8"/>
     </row>
     <row r="224" ht="13.55" customHeight="1">
-      <c r="A224" s="5"/>
-      <c r="B224" s="7"/>
-      <c r="C224" s="5"/>
-      <c r="D224" s="7"/>
-      <c r="E224" s="5"/>
-      <c r="F224" s="7"/>
-      <c r="G224" s="7"/>
-      <c r="H224" s="7"/>
+      <c r="A224" s="6"/>
+      <c r="B224" s="8"/>
+      <c r="C224" s="6"/>
+      <c r="D224" s="8"/>
+      <c r="E224" s="6"/>
+      <c r="F224" s="8"/>
+      <c r="G224" s="8"/>
+      <c r="H224" s="8"/>
+      <c r="I224" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
